--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBFD7D4-35CE-4101-9713-DD6CC6F91E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9000E-79D4-4689-9DA6-2925CFA0E98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9000E-79D4-4689-9DA6-2925CFA0E98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714F2D5E-9907-4515-962E-74C4748B8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>
@@ -751,9 +751,6 @@
     <t>1,1</t>
   </si>
   <si>
-    <t>10000131,2</t>
-  </si>
-  <si>
     <t>10101,10102</t>
   </si>
   <si>
@@ -778,9 +775,6 @@
     <t>团团</t>
   </si>
   <si>
-    <t>10000131,5</t>
-  </si>
-  <si>
     <t>80001005;80001019</t>
   </si>
   <si>
@@ -803,9 +797,6 @@
   </si>
   <si>
     <t>乌贼女士</t>
-  </si>
-  <si>
-    <t>10000131,10</t>
   </si>
   <si>
     <t>80001010;80001001</t>
@@ -997,6 +988,18 @@
   </si>
   <si>
     <t>930101,930102</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000131,2;10000166,2</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000131,5;10000166,5</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000131,10;10000166,10</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2754,7 +2757,7 @@
     <col min="51" max="51" width="10.375" style="2" customWidth="1"/>
     <col min="52" max="53" width="11.375" style="2" customWidth="1"/>
     <col min="54" max="54" width="10.375" style="2" customWidth="1"/>
-    <col min="55" max="55" width="13.125" style="2" customWidth="1"/>
+    <col min="55" max="55" width="22.875" style="2" bestFit="1" customWidth="1"/>
     <col min="56" max="57" width="15.125" style="2" customWidth="1"/>
     <col min="58" max="58" width="25.75" style="2" customWidth="1"/>
     <col min="59" max="59" width="35.375" style="2" customWidth="1"/>
@@ -3069,7 +3072,7 @@
         <v>89</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AR4" s="9" t="s">
         <v>90</v>
@@ -3248,10 +3251,10 @@
         <v>108</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AR5" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AS5" s="5" t="s">
         <v>111</v>
@@ -3463,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="BC6" s="8" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="BD6" s="8">
         <v>0</v>
@@ -3475,13 +3478,13 @@
         <v>80001001</v>
       </c>
       <c r="BG6" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="BH6" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BI6" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -3489,7 +3492,7 @@
         <v>1000201</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="7">
         <v>1000201</v>
@@ -3642,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="BC7" s="8" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="BD7" s="8">
         <v>0</v>
@@ -3651,16 +3654,16 @@
         <v>70000012</v>
       </c>
       <c r="BF7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="BG7" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="BH7" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BG7" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="BH7" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="BI7" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -3668,7 +3671,7 @@
         <v>1000301</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" s="7">
         <v>1000301</v>
@@ -3821,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="BC8" s="8" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="BD8" s="8">
         <v>0</v>
@@ -3833,13 +3836,13 @@
         <v>80001018</v>
       </c>
       <c r="BG8" s="14" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="BH8" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BI8" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -3847,7 +3850,7 @@
         <v>1000401</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="7">
         <v>1000401</v>
@@ -4000,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="BC9" s="8" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="BD9" s="8">
         <v>0</v>
@@ -4012,13 +4015,13 @@
         <v>80001004</v>
       </c>
       <c r="BG9" s="14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="BH9" s="15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="BI9" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4026,7 +4029,7 @@
         <v>1000501</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E10" s="7">
         <v>1000501</v>
@@ -4179,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="BC10" s="8" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="BD10" s="8">
         <v>0</v>
@@ -4188,16 +4191,16 @@
         <v>70000012</v>
       </c>
       <c r="BF10" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BG10" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="BH10" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="BI10" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4205,7 +4208,7 @@
         <v>1000601</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E11" s="7">
         <v>1000601</v>
@@ -4358,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="BC11" s="8" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="BD11" s="8">
         <v>0</v>
@@ -4370,13 +4373,13 @@
         <v>80001006</v>
       </c>
       <c r="BG11" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BH11" s="15" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BI11" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4384,7 +4387,7 @@
         <v>1000701</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E12" s="7">
         <v>1000701</v>
@@ -4537,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="BC12" s="8" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="BD12" s="8">
         <v>0</v>
@@ -4549,13 +4552,13 @@
         <v>80001007</v>
       </c>
       <c r="BG12" s="14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="BH12" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="BI12" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4563,7 +4566,7 @@
         <v>1000801</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E13" s="7">
         <v>1000801</v>
@@ -4716,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="BC13" s="8" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="BD13" s="8">
         <v>0</v>
@@ -4725,16 +4728,16 @@
         <v>70000011</v>
       </c>
       <c r="BF13" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BG13" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="BH13" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BI13" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4742,7 +4745,7 @@
         <v>1000901</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" s="7">
         <v>1000901</v>
@@ -4895,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="BC14" s="8" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="BD14" s="8">
         <v>0</v>
@@ -4907,13 +4910,13 @@
         <v>80001009</v>
       </c>
       <c r="BG14" s="14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="BH14" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="BI14" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -4921,7 +4924,7 @@
         <v>1001001</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E15" s="7">
         <v>1001001</v>
@@ -5074,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="BC15" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD15" s="8">
         <v>0</v>
@@ -5083,16 +5086,16 @@
         <v>70000011</v>
       </c>
       <c r="BF15" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BG15" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="BH15" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="BI15" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5100,7 +5103,7 @@
         <v>1001101</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7">
         <v>1001101</v>
@@ -5253,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="BC16" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD16" s="8">
         <v>0</v>
@@ -5262,16 +5265,16 @@
         <v>70000012</v>
       </c>
       <c r="BF16" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BG16" s="14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="BH16" s="15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="BI16" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5279,7 +5282,7 @@
         <v>1001201</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E17" s="7">
         <v>1001201</v>
@@ -5432,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="BC17" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD17" s="8">
         <v>0</v>
@@ -5441,16 +5444,16 @@
         <v>70000012</v>
       </c>
       <c r="BF17" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BG17" s="14" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="BH17" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BI17" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5458,7 +5461,7 @@
         <v>1001301</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E18" s="7">
         <v>1001301</v>
@@ -5611,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="BC18" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD18" s="8">
         <v>0</v>
@@ -5620,16 +5623,16 @@
         <v>70000011</v>
       </c>
       <c r="BF18" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="BG18" s="14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="BH18" s="15" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="BI18" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5637,7 +5640,7 @@
         <v>1001401</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E19" s="7">
         <v>1001401</v>
@@ -5790,7 +5793,7 @@
         <v>1</v>
       </c>
       <c r="BC19" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD19" s="8">
         <v>0</v>
@@ -5799,16 +5802,16 @@
         <v>70000012</v>
       </c>
       <c r="BF19" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="BG19" s="14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="BH19" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BI19" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5816,7 +5819,7 @@
         <v>1009101</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E20" s="7">
         <v>1009101</v>
@@ -5969,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="BC20" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD20" s="8">
         <v>0</v>
@@ -5978,16 +5981,16 @@
         <v>70000011</v>
       </c>
       <c r="BF20" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="BG20" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="BH20" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="BI20" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -5995,7 +5998,7 @@
         <v>1009201</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E21" s="7">
         <v>1009201</v>
@@ -6148,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="BC21" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD21" s="8">
         <v>0</v>
@@ -6157,16 +6160,16 @@
         <v>70000011</v>
       </c>
       <c r="BF21" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="BG21" s="14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="BH21" s="15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BI21" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -6174,7 +6177,7 @@
         <v>1009301</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E22" s="7">
         <v>1009301</v>
@@ -6327,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="BC22" s="8" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="BD22" s="8">
         <v>0</v>
@@ -6336,16 +6339,16 @@
         <v>70000012</v>
       </c>
       <c r="BF22" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="BG22" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="BH22" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="BI22" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="3:61" ht="20.100000000000001" customHeight="1">
@@ -6353,7 +6356,7 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E23" s="7">
         <v>2000001</v>
@@ -6513,7 +6516,7 @@
         <v>70000011</v>
       </c>
       <c r="BF23" s="18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BG23" s="8">
         <v>0</v>
@@ -6530,7 +6533,7 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E24" s="7">
         <v>2000002</v>
@@ -6690,7 +6693,7 @@
         <v>70000012</v>
       </c>
       <c r="BF24" s="17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="BG24" s="8">
         <v>0</v>
@@ -6707,7 +6710,7 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E25" s="7">
         <v>2000003</v>
@@ -6867,7 +6870,7 @@
         <v>70000011</v>
       </c>
       <c r="BF25" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BG25" s="8">
         <v>0</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1,40 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714F2D5E-9907-4515-962E-74C4748B8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>51Gamer_D01</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -42,7 +49,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -51,7 +58,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>用于宠物界面展示的位置</t>
@@ -60,7 +66,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -68,7 +74,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">在摄像机前修正位置
@@ -76,14 +81,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -91,24 +96,15 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>0</t>
+0</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：普通
@@ -118,7 +114,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1</t>
         </r>
@@ -126,7 +122,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：变异
@@ -136,7 +131,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2</t>
         </r>
@@ -144,21 +139,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：神兽</t>
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>51Gamer_D01:</t>
@@ -167,31 +160,20 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>此字段是玩家用来召唤宠物时,宠物的当前等级</t>
+此字段是玩家用来召唤宠物时,宠物的当前等级</t>
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="O3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者</t>
@@ -201,7 +183,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">:
 </t>
@@ -211,7 +193,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">怪物类型
@@ -222,7 +203,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>0</t>
         </r>
@@ -231,7 +212,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：通用
@@ -242,7 +222,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1</t>
         </r>
@@ -251,7 +231,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：野兽
@@ -262,7 +241,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2</t>
         </r>
@@ -271,7 +250,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：人物
@@ -282,7 +260,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>3</t>
         </r>
@@ -291,41 +269,28 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：恶魔</t>
         </r>
       </text>
     </comment>
-    <comment ref="AY3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="AY3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>当与玩家超过这个范围就返回</t>
+          <t>Administrator:
+当与玩家超过这个范围就返回</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -333,14 +298,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="AZ3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -349,31 +313,20 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>以后改宠物主动攻击模式和被动攻击模式可能会用到</t>
+以后改宠物主动攻击模式和被动攻击模式可能会用到</t>
         </r>
       </text>
     </comment>
-    <comment ref="BF3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="BF3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>51Gamer_D01:</t>
@@ -382,20 +335,10 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> ; 号间隔符</t>
+ ; 号间隔符</t>
         </r>
       </text>
     </comment>
@@ -404,7 +347,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="187">
   <si>
     <t>Id</t>
   </si>
@@ -676,6 +619,9 @@
     <t>Base_MoveSpeed</t>
   </si>
   <si>
+    <t>Base_ActSpeed</t>
+  </si>
+  <si>
     <t>ActDistance</t>
   </si>
   <si>
@@ -751,263 +697,230 @@
     <t>1,1</t>
   </si>
   <si>
+    <t>10000131,2;10000166,2</t>
+  </si>
+  <si>
+    <t>80001010,0.2;80001014,0.2;80001015,0.2</t>
+  </si>
+  <si>
     <t>10101,10102</t>
   </si>
   <si>
+    <t>90,10</t>
+  </si>
+  <si>
     <t>小松鼠</t>
   </si>
   <si>
     <t>80001002;80001013</t>
   </si>
   <si>
+    <t>80001009,0.2;80001025,0.2</t>
+  </si>
+  <si>
     <t>20101,20102</t>
   </si>
   <si>
     <t>小灰狼</t>
   </si>
   <si>
+    <t>80001012,0.2;80001004,0.2;80001007,0.2</t>
+  </si>
+  <si>
     <t>30101,30102</t>
   </si>
   <si>
     <t>仙人掌</t>
   </si>
   <si>
+    <t>80002007,0.2;80001023,0.2;80003001,0.1</t>
+  </si>
+  <si>
+    <t>40101,40102</t>
+  </si>
+  <si>
     <t>团团</t>
   </si>
   <si>
+    <t>10000131,5;10000166,5</t>
+  </si>
+  <si>
     <t>80001005;80001019</t>
   </si>
   <si>
+    <t>80001017,0.2;80001008,0.2;80001021,0.2</t>
+  </si>
+  <si>
+    <t>50101,50102</t>
+  </si>
+  <si>
     <t>企鹅</t>
   </si>
   <si>
+    <t>80001015,0.2;80001010,0.2;80002006,0.2</t>
+  </si>
+  <si>
+    <t>60101,60102</t>
+  </si>
+  <si>
     <t>蛇蛇</t>
   </si>
   <si>
+    <t>80001006,0.2;80002018,0.2;80001022,0.2;80003002,0.1</t>
+  </si>
+  <si>
+    <t>70101,70102</t>
+  </si>
+  <si>
     <t>萝卜头</t>
   </si>
   <si>
     <t>80001008;80001020</t>
   </si>
   <si>
+    <t>80001011,0.2;80002015,0.2;80001024,0.2</t>
+  </si>
+  <si>
     <t>80101,80102</t>
   </si>
   <si>
     <t>雷霆猪</t>
   </si>
   <si>
+    <t>80002001,0.2;80001014,0.2;80001028,0.2;80002022,0.2</t>
+  </si>
+  <si>
+    <t>90101,90102</t>
+  </si>
+  <si>
     <t>乌贼女士</t>
   </si>
   <si>
+    <t>10000131,10;10000166,10</t>
+  </si>
+  <si>
     <t>80001010;80001001</t>
   </si>
   <si>
+    <t>80001002,0.2;80002019,0.2;80003003,0.1</t>
+  </si>
+  <si>
+    <t>100101,100102</t>
+  </si>
+  <si>
     <t>魔法精灵</t>
   </si>
   <si>
     <t>80001011;80001003</t>
   </si>
   <si>
+    <t>80001015,0.2;80002002,0.2;80001027,0.1;80002021,0.1</t>
+  </si>
+  <si>
+    <t>110101,110102</t>
+  </si>
+  <si>
     <t>魔法娃娃</t>
   </si>
   <si>
     <t>80001012;80002025</t>
   </si>
   <si>
+    <t>80002010,0.2;80002003,0.2;80001026,0.1;80002027,0.1</t>
+  </si>
+  <si>
+    <t>120101,120102</t>
+  </si>
+  <si>
     <t>淘气包</t>
   </si>
   <si>
+    <t>80001006;80002004</t>
+  </si>
+  <si>
+    <t>80002016,0.2;80002023,0.2;80003004,0.1</t>
+  </si>
+  <si>
+    <t>130101,130102</t>
+  </si>
+  <si>
     <t>光明天使</t>
   </si>
   <si>
+    <t>80001014;80002009</t>
+  </si>
+  <si>
+    <t>80002013,0.2;80002003,0.2;80003005,0.1</t>
+  </si>
+  <si>
+    <t>140101,140102</t>
+  </si>
+  <si>
+    <t>铁甲勇士</t>
+  </si>
+  <si>
+    <t>80002008;80001016</t>
+  </si>
+  <si>
+    <t>80002017,0.2;80002018,0.2;80003006,0.1</t>
+  </si>
+  <si>
+    <t>910101,910102</t>
+  </si>
+  <si>
+    <t>灵狐之妖</t>
+  </si>
+  <si>
+    <t>80002024;80001020</t>
+  </si>
+  <si>
+    <t>80002014,0.2;80001026,0.2;80003007,0.1</t>
+  </si>
+  <si>
+    <t>920101,920102</t>
+  </si>
+  <si>
+    <t>爱心之灵</t>
+  </si>
+  <si>
+    <t>80002005;80002020</t>
+  </si>
+  <si>
+    <t>80002026,0.2;80001003,0.2;80003008,0.1</t>
+  </si>
+  <si>
+    <t>930101,930102</t>
+  </si>
+  <si>
     <t>神兽:精灵麋鹿</t>
   </si>
   <si>
+    <t>80004005;80004006;80004004;80002008;80002013;80002016;80002017;80002010;80002019;80002023</t>
+  </si>
+  <si>
     <t>神兽:幽光晴晴</t>
   </si>
   <si>
+    <t>80004004;80004008;80004009;80002002;80002003;80002020;80002021;80002024;80002025;80002027</t>
+  </si>
+  <si>
     <t>神兽:仙界魔龙</t>
   </si>
   <si>
-    <t>double</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_ActSpeed</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁甲勇士</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱心之灵</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80001010,0.2;80001014,0.2;80001015,0.2</t>
-  </si>
-  <si>
-    <t>80001009,0.2;80001025,0.2</t>
-  </si>
-  <si>
-    <t>80001012,0.2;80001004,0.2;80001007,0.2</t>
-  </si>
-  <si>
-    <t>80002007,0.2;80001023,0.2;80003001,0.1</t>
-  </si>
-  <si>
-    <t>80001017,0.2;80001008,0.2;80001021,0.2</t>
-  </si>
-  <si>
-    <t>80001015,0.2;80001010,0.2;80002006,0.2</t>
-  </si>
-  <si>
-    <t>80001006,0.2;80002018,0.2;80001022,0.2;80003002,0.1</t>
-  </si>
-  <si>
-    <t>80001011,0.2;80002015,0.2;80001024,0.2</t>
-  </si>
-  <si>
-    <t>80002001,0.2;80001014,0.2;80001028,0.2;80002022,0.2</t>
-  </si>
-  <si>
-    <t>80001002,0.2;80002019,0.2;80003003,0.1</t>
-  </si>
-  <si>
-    <t>80001015,0.2;80002002,0.2;80001027,0.1;80002021,0.1</t>
-  </si>
-  <si>
-    <t>80002010,0.2;80002003,0.2;80001026,0.1;80002027,0.1</t>
-  </si>
-  <si>
-    <t>80002017,0.2;80002018,0.2;80003006,0.1</t>
-  </si>
-  <si>
-    <t>80002008;80001016</t>
-  </si>
-  <si>
-    <t>80004005;80004006;80004004;80002008;80002013;80002016;80002017;80002010;80002019;80002023</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80004004;80004008;80004009;80002002;80002003;80002020;80002021;80002024;80002025;80002027</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>80004004;80004010;80004013;80002001;80002002;80002006;80002011;80002018;80002022;80002028</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>90,10</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵狐之妖</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002005;80002020</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002026,0.2;80001003,0.2;80003008,0.1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002014,0.2;80001026,0.2;80003007,0.1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002024;80001020</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80001014;80002009</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002013,0.2;80002003,0.2;80003005,0.1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80001006;80002004</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002016,0.2;80002023,0.2;80003004,0.1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>40101,40102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>50101,50102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>60101,60102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>70101,70102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>90101,90102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101,100102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>110101,110102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>120101,120102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>130101,130102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>140101,140102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>910101,910102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>920101,920102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>930101,930102</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000131,2;10000166,2</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000131,5;10000166,5</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000131,10;10000166,10</t>
-    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1018,7 +931,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1026,82 +938,226 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1128,31 +1184,259 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79976805932798245"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79976805932798245"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1162,50 +1446,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79976805932798245"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79976805932798245"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79976805932798245"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79976805932798245"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1310,172 +1552,399 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="58">
+  <cellStyleXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1516,77 +1985,127 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="58">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="13" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="10" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+  <cellStyles count="106">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="常规 2 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="常规 2 3" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="常规 2 3 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="常规 2 3 3" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="常规 2 3 3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="常规 2 3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="常规 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="常规 4" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="常规 5" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="常规 5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="常规 5 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="常规 5 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="常规 6" xfId="4" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="注释 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="注释 2 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="注释 2 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="注释 2 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="69"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="73"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="74"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="77"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="78"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="79"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="81"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="82"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="83"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="84"/>
+    <cellStyle name="常规 2" xfId="85"/>
+    <cellStyle name="常规 2 2" xfId="86"/>
+    <cellStyle name="常规 2 3" xfId="87"/>
+    <cellStyle name="常规 2 3 2" xfId="88"/>
+    <cellStyle name="常规 2 3 2 2" xfId="89"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="90"/>
+    <cellStyle name="常规 2 3 2 3" xfId="91"/>
+    <cellStyle name="常规 2 3 3" xfId="92"/>
+    <cellStyle name="常规 2 3 3 2" xfId="93"/>
+    <cellStyle name="常规 2 3 4" xfId="94"/>
+    <cellStyle name="常规 3" xfId="95"/>
+    <cellStyle name="常规 4" xfId="96"/>
+    <cellStyle name="常规 5" xfId="97"/>
+    <cellStyle name="常规 5 2" xfId="98"/>
+    <cellStyle name="常规 5 2 2" xfId="99"/>
+    <cellStyle name="常规 5 3" xfId="100"/>
+    <cellStyle name="常规 6" xfId="101"/>
+    <cellStyle name="注释 2" xfId="102"/>
+    <cellStyle name="注释 2 2" xfId="103"/>
+    <cellStyle name="注释 2 2 2" xfId="104"/>
+    <cellStyle name="注释 2 3" xfId="105"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
@@ -1659,9 +2178,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2732,13 +3248,13 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:JP25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:BI25"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
@@ -2757,7 +3273,7 @@
     <col min="51" max="51" width="10.375" style="2" customWidth="1"/>
     <col min="52" max="53" width="11.375" style="2" customWidth="1"/>
     <col min="54" max="54" width="10.375" style="2" customWidth="1"/>
-    <col min="55" max="55" width="22.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="22.875" style="2" customWidth="1"/>
     <col min="56" max="57" width="15.125" style="2" customWidth="1"/>
     <col min="58" max="58" width="25.75" style="2" customWidth="1"/>
     <col min="59" max="59" width="35.375" style="2" customWidth="1"/>
@@ -2765,13 +3281,13 @@
     <col min="62" max="276" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:61" s="1" customFormat="1" ht="14.25">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="3:3">
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="3:61" ht="13.5" customHeight="1">
+    <row r="2" customHeight="1" spans="4:4">
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="3" ht="20.1" customHeight="1" spans="3:61">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2950,7 +3466,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="4" ht="20.1" customHeight="1" spans="3:61">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -3072,248 +3588,248 @@
         <v>89</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AS4" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AT4" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AU4" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AV4" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AW4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AX4" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AY4" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AZ4" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BA4" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BB4" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BC4" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BD4" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BE4" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF4" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BG4" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BH4" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BI4" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="5" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="5" ht="20.1" customHeight="1" spans="3:61">
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="H5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="J5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="P5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AJ5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="AR5" s="5" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AU5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AW5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AX5" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ5" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BB5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC5" s="5" t="s">
         <v>110</v>
       </c>
       <c r="BD5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BE5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="BE5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="BF5" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG5" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="6" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="6" ht="20.1" customHeight="1" spans="3:61">
       <c r="C6" s="7">
         <v>1000101</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E6" s="7">
         <v>1000101</v>
@@ -3325,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I6" s="8">
         <v>0</v>
@@ -3340,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" s="7">
         <v>0</v>
@@ -3466,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="BC6" s="8" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="BD6" s="8">
         <v>0</v>
@@ -3474,25 +3990,25 @@
       <c r="BE6" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF6" s="17">
+      <c r="BF6" s="8">
         <v>80001001</v>
       </c>
       <c r="BG6" s="14" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="BH6" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BI6" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="7" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="7" ht="20.1" customHeight="1" spans="3:61">
       <c r="C7" s="7">
         <v>1000201</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E7" s="7">
         <v>1000201</v>
@@ -3504,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" s="8">
         <v>0</v>
@@ -3519,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N7" s="7">
         <v>0</v>
@@ -3645,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="BC7" s="8" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="BD7" s="8">
         <v>0</v>
@@ -3654,24 +4170,24 @@
         <v>70000012</v>
       </c>
       <c r="BF7" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BG7" s="14" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="BH7" s="15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BI7" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="8" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="8" ht="20.1" customHeight="1" spans="3:61">
       <c r="C8" s="7">
         <v>1000301</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E8" s="7">
         <v>1000301</v>
@@ -3683,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I8" s="8">
         <v>0</v>
@@ -3698,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N8" s="7">
         <v>0</v>
@@ -3824,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="BC8" s="8" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="BD8" s="8">
         <v>0</v>
@@ -3832,25 +4348,25 @@
       <c r="BE8" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF8" s="17">
+      <c r="BF8" s="8">
         <v>80001018</v>
       </c>
       <c r="BG8" s="14" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="BH8" s="15" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="BI8" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="9" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="9" ht="20.1" customHeight="1" spans="3:61">
       <c r="C9" s="7">
         <v>1000401</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E9" s="7">
         <v>1000401</v>
@@ -3862,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="8">
         <v>0</v>
@@ -3877,7 +4393,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
@@ -3925,7 +4441,7 @@
         <v>0.95</v>
       </c>
       <c r="AC9" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" s="8">
         <v>5000</v>
@@ -4003,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="BC9" s="8" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="BD9" s="8">
         <v>0</v>
@@ -4015,21 +4531,21 @@
         <v>80001004</v>
       </c>
       <c r="BG9" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="BH9" s="15" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="BI9" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="10" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="10" ht="20.1" customHeight="1" spans="3:61">
       <c r="C10" s="7">
         <v>1000501</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E10" s="7">
         <v>1000501</v>
@@ -4041,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="8">
         <v>0</v>
@@ -4056,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
@@ -4104,7 +4620,7 @@
         <v>0.95</v>
       </c>
       <c r="AC10" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AD10" s="8">
         <v>5000</v>
@@ -4146,7 +4662,7 @@
         <v>6</v>
       </c>
       <c r="AQ10" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR10" s="8">
         <v>6</v>
@@ -4182,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="BC10" s="8" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="BD10" s="8">
         <v>0</v>
@@ -4190,25 +4706,25 @@
       <c r="BE10" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF10" s="17" t="s">
-        <v>123</v>
+      <c r="BF10" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="BG10" s="14" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="BH10" s="15" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="BI10" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="11" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="11" ht="20.1" customHeight="1" spans="3:61">
       <c r="C11" s="7">
         <v>1000601</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E11" s="7">
         <v>1000601</v>
@@ -4220,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
@@ -4235,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
@@ -4283,7 +4799,7 @@
         <v>0.95</v>
       </c>
       <c r="AC11" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AD11" s="8">
         <v>5000</v>
@@ -4361,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="BC11" s="8" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="BD11" s="8">
         <v>0</v>
@@ -4373,21 +4889,21 @@
         <v>80001006</v>
       </c>
       <c r="BG11" s="14" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="BH11" s="15" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="BI11" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="12" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="12" ht="20.1" customHeight="1" spans="3:61">
       <c r="C12" s="7">
         <v>1000701</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E12" s="7">
         <v>1000701</v>
@@ -4399,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I12" s="8">
         <v>0</v>
@@ -4414,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="7">
         <v>0</v>
@@ -4462,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="AC12" s="8">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AD12" s="8">
         <v>5000</v>
@@ -4540,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="BC12" s="8" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="BD12" s="8">
         <v>0</v>
@@ -4548,25 +5064,25 @@
       <c r="BE12" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF12" s="17">
+      <c r="BF12" s="8">
         <v>80001007</v>
       </c>
       <c r="BG12" s="14" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="BH12" s="15" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="BI12" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="13" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="13" ht="20.1" customHeight="1" spans="3:61">
       <c r="C13" s="7">
         <v>1000801</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="E13" s="7">
         <v>1000801</v>
@@ -4578,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="8">
         <v>0</v>
@@ -4593,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
@@ -4641,7 +5157,7 @@
         <v>1</v>
       </c>
       <c r="AC13" s="8">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AD13" s="8">
         <v>5000</v>
@@ -4719,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="BC13" s="8" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="BD13" s="8">
         <v>0</v>
@@ -4728,24 +5244,24 @@
         <v>70000011</v>
       </c>
       <c r="BF13" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="BG13" s="14" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="BH13" s="15" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="BI13" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="14" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="14" ht="20.1" customHeight="1" spans="3:61">
       <c r="C14" s="7">
         <v>1000901</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E14" s="7">
         <v>1000901</v>
@@ -4757,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
@@ -4772,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
@@ -4820,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="AC14" s="8">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AD14" s="8">
         <v>5000</v>
@@ -4898,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="BC14" s="8" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="BD14" s="8">
         <v>0</v>
@@ -4910,21 +5426,21 @@
         <v>80001009</v>
       </c>
       <c r="BG14" s="14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="BH14" s="15" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="BI14" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="15" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="15" ht="20.1" customHeight="1" spans="3:61">
       <c r="C15" s="7">
         <v>1001001</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E15" s="7">
         <v>1001001</v>
@@ -4936,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
@@ -4951,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
@@ -5077,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="BC15" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD15" s="8">
         <v>0</v>
@@ -5086,24 +5602,24 @@
         <v>70000011</v>
       </c>
       <c r="BF15" s="8" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="BG15" s="14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="BH15" s="15" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="BI15" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="16" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="16" ht="20.1" customHeight="1" spans="3:61">
       <c r="C16" s="7">
         <v>1001101</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="E16" s="7">
         <v>1001101</v>
@@ -5115,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I16" s="8">
         <v>0</v>
@@ -5130,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N16" s="7">
         <v>0</v>
@@ -5220,7 +5736,7 @@
         <v>6</v>
       </c>
       <c r="AQ16" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR16" s="8">
         <v>6</v>
@@ -5256,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="BC16" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD16" s="8">
         <v>0</v>
@@ -5265,24 +5781,24 @@
         <v>70000012</v>
       </c>
       <c r="BF16" s="8" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="BG16" s="14" t="s">
         <v>155</v>
       </c>
       <c r="BH16" s="15" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="BI16" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="17" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="17" ht="20.1" customHeight="1" spans="3:61">
       <c r="C17" s="7">
         <v>1001201</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="E17" s="7">
         <v>1001201</v>
@@ -5294,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I17" s="8">
         <v>0</v>
@@ -5309,7 +5825,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N17" s="7">
         <v>0</v>
@@ -5399,7 +5915,7 @@
         <v>6</v>
       </c>
       <c r="AQ17" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR17" s="8">
         <v>6</v>
@@ -5435,7 +5951,7 @@
         <v>1</v>
       </c>
       <c r="BC17" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD17" s="8">
         <v>0</v>
@@ -5444,24 +5960,24 @@
         <v>70000012</v>
       </c>
       <c r="BF17" s="8" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="BG17" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="BH17" s="15" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="BI17" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="18" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="18" ht="20.1" customHeight="1" spans="3:61">
       <c r="C18" s="7">
         <v>1001301</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E18" s="7">
         <v>1001301</v>
@@ -5473,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I18" s="8">
         <v>0</v>
@@ -5488,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N18" s="7">
         <v>0</v>
@@ -5614,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="BC18" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD18" s="8">
         <v>0</v>
@@ -5623,24 +6139,24 @@
         <v>70000011</v>
       </c>
       <c r="BF18" s="8" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="BG18" s="14" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="BH18" s="15" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="BI18" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="19" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="19" ht="20.1" customHeight="1" spans="3:61">
       <c r="C19" s="7">
         <v>1001401</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="E19" s="7">
         <v>1001401</v>
@@ -5652,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I19" s="8">
         <v>0</v>
@@ -5667,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N19" s="7">
         <v>0</v>
@@ -5757,7 +6273,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR19" s="8">
         <v>6</v>
@@ -5793,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="BC19" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD19" s="8">
         <v>0</v>
@@ -5802,24 +6318,24 @@
         <v>70000012</v>
       </c>
       <c r="BF19" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="BG19" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="BH19" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="BG19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="BH19" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="BI19" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="20" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="20" ht="20.1" customHeight="1" spans="3:61">
       <c r="C20" s="7">
         <v>1009101</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="E20" s="7">
         <v>1009101</v>
@@ -5831,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I20" s="8">
         <v>0</v>
@@ -5846,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
@@ -5972,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="BC20" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD20" s="8">
         <v>0</v>
@@ -5981,24 +6497,24 @@
         <v>70000011</v>
       </c>
       <c r="BF20" s="8" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="BG20" s="14" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="BH20" s="15" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="BI20" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="21" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="21" ht="20.1" customHeight="1" spans="3:61">
       <c r="C21" s="7">
         <v>1009201</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E21" s="7">
         <v>1009201</v>
@@ -6010,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I21" s="8">
         <v>0</v>
@@ -6025,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N21" s="7">
         <v>0</v>
@@ -6151,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="BC21" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD21" s="8">
         <v>0</v>
@@ -6160,24 +6676,24 @@
         <v>70000011</v>
       </c>
       <c r="BF21" s="8" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="BG21" s="14" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="BH21" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="BI21" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="22" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="22" ht="20.1" customHeight="1" spans="3:61">
       <c r="C22" s="7">
         <v>1009301</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="E22" s="7">
         <v>1009301</v>
@@ -6189,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I22" s="8">
         <v>0</v>
@@ -6204,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N22" s="7">
         <v>0</v>
@@ -6294,7 +6810,7 @@
         <v>6</v>
       </c>
       <c r="AQ22" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR22" s="8">
         <v>6</v>
@@ -6330,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="BC22" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="BD22" s="8">
         <v>0</v>
@@ -6339,24 +6855,24 @@
         <v>70000012</v>
       </c>
       <c r="BF22" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="BG22" s="14" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="BH22" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="BI22" s="15" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="23" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="23" ht="20.1" customHeight="1" spans="3:61">
       <c r="C23" s="7">
         <v>2000001</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="E23" s="7">
         <v>2000001</v>
@@ -6368,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I23" s="8">
         <v>2</v>
@@ -6383,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N23" s="7">
         <v>0</v>
@@ -6515,8 +7031,8 @@
       <c r="BE23" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF23" s="18" t="s">
-        <v>159</v>
+      <c r="BF23" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="BG23" s="8">
         <v>0</v>
@@ -6524,16 +7040,16 @@
       <c r="BH23" s="15">
         <v>200001</v>
       </c>
-      <c r="BI23" s="16">
+      <c r="BI23" s="17">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="24" ht="20.1" customHeight="1" spans="3:61">
       <c r="C24" s="7">
         <v>2000002</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="E24" s="7">
         <v>2000002</v>
@@ -6545,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I24" s="8">
         <v>2</v>
@@ -6560,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N24" s="7">
         <v>0</v>
@@ -6650,7 +7166,7 @@
         <v>6</v>
       </c>
       <c r="AQ24" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AR24" s="8">
         <v>6</v>
@@ -6692,8 +7208,8 @@
       <c r="BE24" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF24" s="17" t="s">
-        <v>160</v>
+      <c r="BF24" s="18" t="s">
+        <v>184</v>
       </c>
       <c r="BG24" s="8">
         <v>0</v>
@@ -6701,16 +7217,16 @@
       <c r="BH24" s="15">
         <v>200002</v>
       </c>
-      <c r="BI24" s="16">
+      <c r="BI24" s="17">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:61" ht="20.100000000000001" customHeight="1">
+    <row r="25" ht="20.1" customHeight="1" spans="3:61">
       <c r="C25" s="7">
         <v>2000003</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="E25" s="7">
         <v>2000003</v>
@@ -6722,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I25" s="8">
         <v>2</v>
@@ -6737,7 +7253,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N25" s="7">
         <v>0</v>
@@ -6869,26 +7385,25 @@
       <c r="BE25" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF25" s="17" t="s">
-        <v>161</v>
+      <c r="BF25" s="18" t="s">
+        <v>186</v>
       </c>
       <c r="BG25" s="8">
         <v>0</v>
       </c>
-      <c r="BH25" s="16">
+      <c r="BH25" s="17">
         <v>200003</v>
       </c>
-      <c r="BI25" s="16">
+      <c r="BI25" s="17">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -697,7 +697,7 @@
     <t>1,1</t>
   </si>
   <si>
-    <t>10000131,2;10000166,2</t>
+    <t>10000131;2@10000166;2</t>
   </si>
   <si>
     <t>80001010,0.2;80001014,0.2;80001015,0.2</t>
@@ -742,7 +742,7 @@
     <t>团团</t>
   </si>
   <si>
-    <t>10000131,5;10000166,5</t>
+    <t>10000131;5@10000166;5</t>
   </si>
   <si>
     <t>80001005;80001019</t>
@@ -796,7 +796,7 @@
     <t>乌贼女士</t>
   </si>
   <si>
-    <t>10000131,10;10000166,10</t>
+    <t>10000131;10@10000166;10</t>
   </si>
   <si>
     <t>80001010;80001001</t>
@@ -920,7 +920,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1112,31 +1112,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1147,7 +1123,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1156,8 +1143,14 @@
       <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="49">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1404,48 +1397,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -1782,165 +1733,165 @@
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1,47 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF09DD98-60F3-4C0B-92CF-C609F9DD1C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>51Gamer_D01</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -49,7 +42,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -58,6 +51,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>用于宠物界面展示的位置</t>
@@ -66,7 +60,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -74,6 +68,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">在摄像机前修正位置
@@ -81,14 +76,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -96,7 +91,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 0</t>
@@ -105,6 +100,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：普通
@@ -114,7 +110,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>1</t>
         </r>
@@ -122,6 +118,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：变异
@@ -131,7 +128,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>2</t>
         </r>
@@ -139,19 +136,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：神兽</t>
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1">
+    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>51Gamer_D01:</t>
@@ -160,6 +159,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -167,13 +167,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="2">
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者</t>
@@ -183,7 +184,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">:
 </t>
@@ -193,6 +194,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">怪物类型
@@ -203,7 +205,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>0</t>
         </r>
@@ -212,6 +214,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：通用
@@ -222,7 +225,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>1</t>
         </r>
@@ -231,6 +234,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：野兽
@@ -241,7 +245,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>2</t>
         </r>
@@ -250,6 +254,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：人物
@@ -260,7 +265,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>3</t>
         </r>
@@ -269,19 +274,21 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：恶魔</t>
         </r>
       </text>
     </comment>
-    <comment ref="AY3" authorId="0">
+    <comment ref="AZ3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:
@@ -291,6 +298,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -298,13 +306,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ3" authorId="0">
+    <comment ref="BA3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -313,6 +322,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -320,13 +330,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="BF3" authorId="1">
+    <comment ref="BG3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>51Gamer_D01:</t>
@@ -335,6 +346,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -347,7 +359,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="209">
   <si>
     <t>Id</t>
   </si>
@@ -908,19 +920,84 @@
   </si>
   <si>
     <t>80004004;80004010;80004013;80002001;80002002;80002006;80002011;80002018;80002022;80002028</t>
+  </si>
+  <si>
+    <t>PetName_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little Duck Duck</t>
+  </si>
+  <si>
+    <t>Little Squirrel</t>
+  </si>
+  <si>
+    <t>Little gray wolf</t>
+  </si>
+  <si>
+    <t>Cactus</t>
+  </si>
+  <si>
+    <t>Tuantuan</t>
+  </si>
+  <si>
+    <t>Penguin</t>
+  </si>
+  <si>
+    <t>Snake Snake</t>
+  </si>
+  <si>
+    <t>Rabbit Head</t>
+  </si>
+  <si>
+    <t>Thunder Pig</t>
+  </si>
+  <si>
+    <t>Octopus Lady</t>
+  </si>
+  <si>
+    <t>Magic Elves</t>
+  </si>
+  <si>
+    <t>Magic Doll</t>
+  </si>
+  <si>
+    <t>Naughty Guy</t>
+  </si>
+  <si>
+    <t>Light Angel</t>
+  </si>
+  <si>
+    <t>Ironclad Warrior</t>
+  </si>
+  <si>
+    <t>Spirit Fox Demon</t>
+  </si>
+  <si>
+    <t>Loving Spirit</t>
+  </si>
+  <si>
+    <t>Legendary: Elf Deer</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary: Yuguang Qingqing</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary: Immortal Realm</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="33">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -931,6 +1008,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -938,219 +1016,82 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1183,222 +1124,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799768059327982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799768059327982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799768059327982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799768059327982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799768059327982"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799768059327982"/>
+        <fgColor theme="9" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1503,288 +1300,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="106">
+  <cellStyleXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1796,49 +1330,85 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -1867,7 +1437,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1895,7 +1465,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1936,127 +1506,77 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="106">
+  <cellStyles count="58">
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="51"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="55"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="57"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="61"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="63"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="65"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="66"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="68"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="69"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="70"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="71"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="72"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="73"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="74"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="75"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="76"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="77"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="78"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="79"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="80"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="81"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="82"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="83"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="84"/>
-    <cellStyle name="常规 2" xfId="85"/>
-    <cellStyle name="常规 2 2" xfId="86"/>
-    <cellStyle name="常规 2 3" xfId="87"/>
-    <cellStyle name="常规 2 3 2" xfId="88"/>
-    <cellStyle name="常规 2 3 2 2" xfId="89"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="90"/>
-    <cellStyle name="常规 2 3 2 3" xfId="91"/>
-    <cellStyle name="常规 2 3 3" xfId="92"/>
-    <cellStyle name="常规 2 3 3 2" xfId="93"/>
-    <cellStyle name="常规 2 3 4" xfId="94"/>
-    <cellStyle name="常规 3" xfId="95"/>
-    <cellStyle name="常规 4" xfId="96"/>
-    <cellStyle name="常规 5" xfId="97"/>
-    <cellStyle name="常规 5 2" xfId="98"/>
-    <cellStyle name="常规 5 2 2" xfId="99"/>
-    <cellStyle name="常规 5 3" xfId="100"/>
-    <cellStyle name="常规 6" xfId="101"/>
-    <cellStyle name="注释 2" xfId="102"/>
-    <cellStyle name="注释 2 2" xfId="103"/>
-    <cellStyle name="注释 2 2 2" xfId="104"/>
-    <cellStyle name="注释 2 3" xfId="105"/>
+    <cellStyle name="常规 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="常规 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="常规 2 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="常规 2 3 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="常规 2 3 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="常规 2 3 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="常规 2 3 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="常规 2 3 3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="常规 2 3 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="常规 3" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="常规 4" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="常规 5" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="常规 5 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="常规 5 2 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="常规 5 3" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="常规 6" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="注释 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="注释 2 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="注释 2 2 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="注释 2 3" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
@@ -2129,6 +1649,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3199,46 +2722,49 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C1:BI25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:JQ25"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="11.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20" style="2" customWidth="1"/>
-    <col min="9" max="13" width="11.875" style="2" customWidth="1"/>
-    <col min="14" max="15" width="15.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="16.125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.375" style="2" customWidth="1"/>
-    <col min="18" max="25" width="13.125" style="2" customWidth="1"/>
-    <col min="26" max="27" width="18" style="2" customWidth="1"/>
-    <col min="28" max="29" width="20" style="2" customWidth="1"/>
-    <col min="30" max="49" width="15.625" style="2" customWidth="1"/>
-    <col min="50" max="50" width="13.375" style="2" customWidth="1"/>
-    <col min="51" max="51" width="10.375" style="2" customWidth="1"/>
-    <col min="52" max="53" width="11.375" style="2" customWidth="1"/>
-    <col min="54" max="54" width="10.375" style="2" customWidth="1"/>
-    <col min="55" max="55" width="22.875" style="2" customWidth="1"/>
-    <col min="56" max="57" width="15.125" style="2" customWidth="1"/>
-    <col min="58" max="58" width="25.75" style="2" customWidth="1"/>
-    <col min="59" max="59" width="35.375" style="2" customWidth="1"/>
-    <col min="60" max="61" width="25.5" style="2" customWidth="1"/>
-    <col min="62" max="276" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="14.125" style="2" customWidth="1"/>
+    <col min="6" max="8" width="11.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20" style="2" customWidth="1"/>
+    <col min="10" max="14" width="11.875" style="2" customWidth="1"/>
+    <col min="15" max="16" width="15.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="16.125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="12.375" style="2" customWidth="1"/>
+    <col min="19" max="26" width="13.125" style="2" customWidth="1"/>
+    <col min="27" max="28" width="18" style="2" customWidth="1"/>
+    <col min="29" max="30" width="20" style="2" customWidth="1"/>
+    <col min="31" max="50" width="15.625" style="2" customWidth="1"/>
+    <col min="51" max="51" width="13.375" style="2" customWidth="1"/>
+    <col min="52" max="52" width="10.375" style="2" customWidth="1"/>
+    <col min="53" max="54" width="11.375" style="2" customWidth="1"/>
+    <col min="55" max="55" width="10.375" style="2" customWidth="1"/>
+    <col min="56" max="56" width="22.875" style="2" customWidth="1"/>
+    <col min="57" max="58" width="15.125" style="2" customWidth="1"/>
+    <col min="59" max="59" width="25.75" style="2" customWidth="1"/>
+    <col min="60" max="60" width="35.375" style="2" customWidth="1"/>
+    <col min="61" max="62" width="25.5" style="2" customWidth="1"/>
+    <col min="63" max="277" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="3:3">
+    <row r="1" spans="3:62" s="1" customFormat="1" ht="14.25">
       <c r="C1" s="3"/>
     </row>
-    <row r="2" customHeight="1" spans="4:4">
+    <row r="2" spans="3:62" ht="13.5" customHeight="1">
       <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:61">
+    <row r="3" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -3246,46 +2772,46 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>14</v>
@@ -3297,127 +2823,130 @@
         <v>14</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC3" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AD3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AF3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AG3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG3" s="5" t="s">
+      <c r="AH3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AH3" s="5" t="s">
+      <c r="AI3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AI3" s="5" t="s">
+      <c r="AJ3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AJ3" s="5" t="s">
+      <c r="AK3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AK3" s="5" t="s">
+      <c r="AL3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AL3" s="5" t="s">
+      <c r="AM3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AM3" s="5" t="s">
+      <c r="AN3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AN3" s="5" t="s">
+      <c r="AO3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AO3" s="5" t="s">
+      <c r="AP3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AP3" s="5" t="s">
+      <c r="AQ3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AQ3" s="5" t="s">
+      <c r="AR3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AR3" s="5" t="s">
+      <c r="AS3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AS3" s="5" t="s">
+      <c r="AT3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AT3" s="5" t="s">
+      <c r="AU3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AU3" s="5" t="s">
+      <c r="AV3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AV3" s="5" t="s">
+      <c r="AW3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AW3" s="5" t="s">
+      <c r="AX3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AX3" s="10" t="s">
+      <c r="AY3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AY3" s="5" t="s">
+      <c r="AZ3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AZ3" s="10" t="s">
+      <c r="BA3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="BA3" s="5" t="s">
+      <c r="BB3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="BB3" s="5" t="s">
+      <c r="BC3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="BC3" s="5" t="s">
+      <c r="BD3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="BD3" s="5" t="s">
+      <c r="BE3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="BE3" s="5" t="s">
+      <c r="BF3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="BF3" s="5" t="s">
+      <c r="BG3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="BG3" s="5" t="s">
+      <c r="BH3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="BH3" s="13" t="s">
+      <c r="BI3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="BI3" s="13" t="s">
+      <c r="BJ3" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:61">
+    <row r="4" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -3425,178 +2954,181 @@
         <v>51</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AD4" s="9" t="s">
+      <c r="AE4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="AI4" s="5" t="s">
+      <c r="AJ4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AL4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AL4" s="5" t="s">
+      <c r="AM4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AO4" s="9" t="s">
+      <c r="AP4" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AQ4" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AR4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AR4" s="9" t="s">
+      <c r="AS4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AS4" s="9" t="s">
+      <c r="AT4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AT4" s="5" t="s">
+      <c r="AU4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AU4" s="5" t="s">
+      <c r="AV4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AV4" s="5" t="s">
+      <c r="AW4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AW4" s="5" t="s">
+      <c r="AX4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="AX4" s="11" t="s">
+      <c r="AY4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="AY4" s="9" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AZ4" s="11" t="s">
+      <c r="BA4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="BA4" s="9" t="s">
+      <c r="BB4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BB4" s="9" t="s">
+      <c r="BC4" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="5" t="s">
+      <c r="BD4" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="9" t="s">
+      <c r="BE4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BF4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BG4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BH4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="BH4" s="9" t="s">
+      <c r="BI4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="BI4" s="9" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:61">
+    <row r="5" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="4" t="s">
         <v>109</v>
       </c>
@@ -3607,16 +3139,16 @@
         <v>110</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>109</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>109</v>
@@ -3628,13 +3160,13 @@
         <v>109</v>
       </c>
       <c r="M5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>109</v>
@@ -3673,13 +3205,13 @@
         <v>109</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC5" s="5" t="s">
         <v>112</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AE5" s="5" t="s">
         <v>109</v>
@@ -3694,19 +3226,19 @@
         <v>109</v>
       </c>
       <c r="AI5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="AJ5" s="5" t="s">
+      <c r="AK5" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="AK5" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>112</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>109</v>
@@ -3718,7 +3250,7 @@
         <v>109</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AR5" s="5" t="s">
         <v>112</v>
@@ -3738,155 +3270,158 @@
       <c r="AW5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="AX5" s="10" t="s">
+      <c r="AX5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY5" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="AY5" s="5" t="s">
+      <c r="AZ5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="AZ5" s="10" t="s">
+      <c r="BA5" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="BA5" s="5" t="s">
+      <c r="BB5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="BB5" s="5" t="s">
+      <c r="BC5" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="BC5" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="BD5" s="5" t="s">
         <v>110</v>
       </c>
       <c r="BE5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BF5" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="BF5" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="BG5" s="5" t="s">
         <v>110</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI5" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="BJ5" s="5" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:61">
+    <row r="6" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="7">
         <v>1000101</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="7">
-        <v>1000101</v>
+      <c r="E6" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="F6" s="7">
         <v>1000101</v>
       </c>
       <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8" t="s">
+        <v>1000101</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
       <c r="J6" s="8">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
         <v>1</v>
       </c>
       <c r="L6" s="7">
         <v>1</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="7">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
       <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="8">
         <v>1500</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="R6" s="8">
         <v>2500</v>
       </c>
-      <c r="R6" s="8">
-        <v>1000</v>
-      </c>
       <c r="S6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T6" s="8">
         <v>1500</v>
       </c>
-      <c r="T6" s="8">
-        <v>1000</v>
-      </c>
       <c r="U6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V6" s="8">
         <v>1500</v>
       </c>
-      <c r="V6" s="8">
-        <v>1000</v>
-      </c>
       <c r="W6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X6" s="8">
         <v>1200</v>
       </c>
-      <c r="X6" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z6" s="8">
         <v>1200</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="AA6" s="8">
         <v>1500</v>
       </c>
-      <c r="AA6" s="8">
+      <c r="AB6" s="8">
         <v>3000</v>
       </c>
-      <c r="AB6" s="8">
+      <c r="AC6" s="8">
         <v>0.9</v>
       </c>
-      <c r="AC6" s="8">
+      <c r="AD6" s="8">
         <v>1.05</v>
       </c>
-      <c r="AD6" s="8">
+      <c r="AE6" s="8">
         <v>5000</v>
       </c>
-      <c r="AE6" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF6" s="8">
         <v>1000</v>
       </c>
       <c r="AG6" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH6" s="8">
         <v>350</v>
       </c>
       <c r="AI6" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ6" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ6" s="8">
-        <v>0</v>
-      </c>
       <c r="AK6" s="8">
         <v>0</v>
       </c>
       <c r="AL6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM6" s="8">
-        <v>0</v>
-      </c>
       <c r="AN6" s="8">
         <v>0</v>
       </c>
@@ -3894,178 +3429,181 @@
         <v>0</v>
       </c>
       <c r="AP6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="8">
         <v>6</v>
       </c>
-      <c r="AQ6" s="8">
-        <v>1</v>
-      </c>
       <c r="AR6" s="8">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="8">
         <v>2</v>
       </c>
-      <c r="AS6" s="8">
+      <c r="AT6" s="8">
         <v>132</v>
-      </c>
-      <c r="AT6" s="8">
-        <v>25</v>
       </c>
       <c r="AU6" s="8">
         <v>25</v>
       </c>
       <c r="AV6" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW6" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX6" s="12">
+      <c r="AX6" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY6" s="12">
         <v>3</v>
       </c>
-      <c r="AY6" s="8">
+      <c r="AZ6" s="8">
         <v>15</v>
       </c>
-      <c r="AZ6" s="12">
+      <c r="BA6" s="12">
         <v>10</v>
       </c>
-      <c r="BA6" s="8">
+      <c r="BB6" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB6" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC6" s="8" t="s">
+      <c r="BC6" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BD6" s="8">
-        <v>0</v>
-      </c>
       <c r="BE6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF6" s="8">
+      <c r="BG6" s="8">
         <v>80001001</v>
       </c>
-      <c r="BG6" s="14" t="s">
+      <c r="BH6" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="BH6" s="15" t="s">
+      <c r="BI6" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BI6" s="15" t="s">
+      <c r="BJ6" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:61">
+    <row r="7" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="7">
         <v>1000201</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="7">
-        <v>1000201</v>
+      <c r="E7" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="F7" s="7">
         <v>1000201</v>
       </c>
       <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="s">
+        <v>1000201</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
       <c r="J7" s="8">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
         <v>1</v>
       </c>
       <c r="L7" s="7">
         <v>1</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N7" s="7">
-        <v>0</v>
-      </c>
       <c r="O7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8">
         <v>1500</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="R7" s="8">
         <v>2500</v>
       </c>
-      <c r="R7" s="8">
-        <v>1000</v>
-      </c>
       <c r="S7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T7" s="8">
         <v>1500</v>
       </c>
-      <c r="T7" s="8">
-        <v>1000</v>
-      </c>
       <c r="U7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V7" s="8">
         <v>1500</v>
       </c>
-      <c r="V7" s="8">
-        <v>1000</v>
-      </c>
       <c r="W7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X7" s="8">
         <v>1200</v>
       </c>
-      <c r="X7" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z7" s="8">
         <v>1200</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="AA7" s="8">
         <v>1500</v>
       </c>
-      <c r="AA7" s="8">
+      <c r="AB7" s="8">
         <v>3000</v>
       </c>
-      <c r="AB7" s="8">
+      <c r="AC7" s="8">
         <v>0.9</v>
       </c>
-      <c r="AC7" s="8">
+      <c r="AD7" s="8">
         <v>1.05</v>
       </c>
-      <c r="AD7" s="8">
+      <c r="AE7" s="8">
         <v>5000</v>
       </c>
-      <c r="AE7" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF7" s="8">
         <v>1000</v>
       </c>
       <c r="AG7" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH7" s="8">
         <v>350</v>
       </c>
       <c r="AI7" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ7" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ7" s="8">
-        <v>0</v>
-      </c>
       <c r="AK7" s="8">
         <v>0</v>
       </c>
       <c r="AL7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM7" s="8">
-        <v>0</v>
-      </c>
       <c r="AN7" s="8">
         <v>0</v>
       </c>
@@ -4073,178 +3611,181 @@
         <v>0</v>
       </c>
       <c r="AP7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="8">
         <v>6</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AR7" s="8">
         <v>1.2</v>
       </c>
-      <c r="AR7" s="8">
+      <c r="AS7" s="8">
         <v>6</v>
       </c>
-      <c r="AS7" s="8">
+      <c r="AT7" s="8">
         <v>132</v>
-      </c>
-      <c r="AT7" s="8">
-        <v>25</v>
       </c>
       <c r="AU7" s="8">
         <v>25</v>
       </c>
       <c r="AV7" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW7" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX7" s="12">
+      <c r="AX7" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY7" s="12">
         <v>3</v>
       </c>
-      <c r="AY7" s="8">
+      <c r="AZ7" s="8">
         <v>15</v>
       </c>
-      <c r="AZ7" s="12">
+      <c r="BA7" s="12">
         <v>10</v>
       </c>
-      <c r="BA7" s="8">
+      <c r="BB7" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB7" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="8" t="s">
+      <c r="BC7" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BD7" s="8">
-        <v>0</v>
-      </c>
       <c r="BE7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF7" s="8" t="s">
+      <c r="BG7" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="BG7" s="14" t="s">
+      <c r="BH7" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="BH7" s="15" t="s">
+      <c r="BI7" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="BI7" s="15" t="s">
+      <c r="BJ7" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:61">
+    <row r="8" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C8" s="7">
         <v>1000301</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="7">
-        <v>1000301</v>
+      <c r="E8" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="F8" s="7">
         <v>1000301</v>
       </c>
       <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8" t="s">
+        <v>1000301</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
       <c r="J8" s="8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
         <v>1</v>
       </c>
       <c r="L8" s="7">
         <v>1</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="7">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="7">
-        <v>0</v>
-      </c>
       <c r="O8" s="7">
-        <v>1</v>
-      </c>
-      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8">
         <v>1500</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="R8" s="8">
         <v>2500</v>
       </c>
-      <c r="R8" s="8">
-        <v>1000</v>
-      </c>
       <c r="S8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T8" s="8">
         <v>1500</v>
       </c>
-      <c r="T8" s="8">
-        <v>1000</v>
-      </c>
       <c r="U8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V8" s="8">
         <v>1500</v>
       </c>
-      <c r="V8" s="8">
-        <v>1000</v>
-      </c>
       <c r="W8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X8" s="8">
         <v>1200</v>
       </c>
-      <c r="X8" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z8" s="8">
         <v>1200</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="AA8" s="8">
         <v>1500</v>
       </c>
-      <c r="AA8" s="8">
+      <c r="AB8" s="8">
         <v>3000</v>
       </c>
-      <c r="AB8" s="8">
+      <c r="AC8" s="8">
         <v>0.9</v>
       </c>
-      <c r="AC8" s="8">
+      <c r="AD8" s="8">
         <v>1.05</v>
       </c>
-      <c r="AD8" s="8">
+      <c r="AE8" s="8">
         <v>5000</v>
       </c>
-      <c r="AE8" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF8" s="8">
         <v>1000</v>
       </c>
       <c r="AG8" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH8" s="8">
         <v>350</v>
       </c>
       <c r="AI8" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ8" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ8" s="8">
-        <v>0</v>
-      </c>
       <c r="AK8" s="8">
         <v>0</v>
       </c>
       <c r="AL8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM8" s="8">
-        <v>0</v>
-      </c>
       <c r="AN8" s="8">
         <v>0</v>
       </c>
@@ -4252,178 +3793,181 @@
         <v>0</v>
       </c>
       <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="8">
         <v>6</v>
       </c>
-      <c r="AQ8" s="8">
-        <v>1</v>
-      </c>
       <c r="AR8" s="8">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="8">
         <v>2</v>
       </c>
-      <c r="AS8" s="8">
+      <c r="AT8" s="8">
         <v>132</v>
-      </c>
-      <c r="AT8" s="8">
-        <v>25</v>
       </c>
       <c r="AU8" s="8">
         <v>25</v>
       </c>
       <c r="AV8" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW8" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX8" s="12">
+      <c r="AX8" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY8" s="12">
         <v>3</v>
       </c>
-      <c r="AY8" s="8">
+      <c r="AZ8" s="8">
         <v>15</v>
       </c>
-      <c r="AZ8" s="12">
+      <c r="BA8" s="12">
         <v>10</v>
       </c>
-      <c r="BA8" s="8">
+      <c r="BB8" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB8" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC8" s="8" t="s">
+      <c r="BC8" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BD8" s="8">
-        <v>0</v>
-      </c>
       <c r="BE8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF8" s="8">
+      <c r="BG8" s="8">
         <v>80001018</v>
       </c>
-      <c r="BG8" s="14" t="s">
+      <c r="BH8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="BH8" s="15" t="s">
+      <c r="BI8" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="BI8" s="15" t="s">
+      <c r="BJ8" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:61">
+    <row r="9" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C9" s="7">
         <v>1000401</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="7">
-        <v>1000401</v>
+      <c r="E9" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="F9" s="7">
         <v>1000401</v>
       </c>
       <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="s">
+        <v>1000401</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
       <c r="J9" s="8">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1</v>
+      </c>
+      <c r="L9" s="7">
         <v>2</v>
       </c>
-      <c r="L9" s="7">
-        <v>1</v>
-      </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="7">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N9" s="7">
-        <v>0</v>
-      </c>
       <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="8">
         <v>1500</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="R9" s="8">
         <v>3000</v>
       </c>
-      <c r="R9" s="8">
-        <v>1000</v>
-      </c>
       <c r="S9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T9" s="8">
         <v>1300</v>
       </c>
-      <c r="T9" s="8">
-        <v>1000</v>
-      </c>
       <c r="U9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V9" s="8">
         <v>1300</v>
       </c>
-      <c r="V9" s="8">
-        <v>1000</v>
-      </c>
       <c r="W9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X9" s="8">
         <v>1500</v>
       </c>
-      <c r="X9" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y9" s="8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z9" s="8">
         <v>1500</v>
       </c>
       <c r="AA9" s="8">
+        <v>1500</v>
+      </c>
+      <c r="AB9" s="8">
         <v>3000</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AC9" s="8">
         <v>0.95</v>
       </c>
-      <c r="AC9" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AD9" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AE9" s="8">
         <v>5000</v>
       </c>
-      <c r="AE9" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF9" s="8">
         <v>1000</v>
       </c>
       <c r="AG9" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH9" s="8">
         <v>350</v>
       </c>
       <c r="AI9" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ9" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ9" s="8">
-        <v>0</v>
-      </c>
       <c r="AK9" s="8">
         <v>0</v>
       </c>
       <c r="AL9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM9" s="8">
-        <v>0</v>
-      </c>
       <c r="AN9" s="8">
         <v>0</v>
       </c>
@@ -4431,178 +3975,181 @@
         <v>0</v>
       </c>
       <c r="AP9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="8">
         <v>6</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AR9" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR9" s="8">
+      <c r="AS9" s="8">
         <v>2</v>
       </c>
-      <c r="AS9" s="8">
+      <c r="AT9" s="8">
         <v>132</v>
-      </c>
-      <c r="AT9" s="8">
-        <v>25</v>
       </c>
       <c r="AU9" s="8">
         <v>25</v>
       </c>
       <c r="AV9" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW9" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX9" s="12">
+      <c r="AX9" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY9" s="12">
         <v>3</v>
       </c>
-      <c r="AY9" s="8">
+      <c r="AZ9" s="8">
         <v>15</v>
       </c>
-      <c r="AZ9" s="12">
+      <c r="BA9" s="12">
         <v>10</v>
       </c>
-      <c r="BA9" s="8">
+      <c r="BB9" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB9" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="8" t="s">
+      <c r="BC9" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BD9" s="8">
-        <v>0</v>
-      </c>
       <c r="BE9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF9" s="8">
+      <c r="BG9" s="8">
         <v>80001004</v>
       </c>
-      <c r="BG9" s="14" t="s">
+      <c r="BH9" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="BH9" s="15" t="s">
+      <c r="BI9" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="BI9" s="15" t="s">
+      <c r="BJ9" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:61">
+    <row r="10" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C10" s="7">
         <v>1000501</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="7">
-        <v>1000501</v>
+      <c r="E10" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="F10" s="7">
         <v>1000501</v>
       </c>
       <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="s">
+        <v>1000501</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="8">
-        <v>0</v>
-      </c>
       <c r="J10" s="8">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="7">
         <v>2</v>
       </c>
-      <c r="L10" s="7">
-        <v>1</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="7">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
       <c r="O10" s="7">
-        <v>1</v>
-      </c>
-      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8">
         <v>1500</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="R10" s="8">
         <v>3000</v>
       </c>
-      <c r="R10" s="8">
-        <v>1000</v>
-      </c>
       <c r="S10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T10" s="8">
         <v>1400</v>
       </c>
-      <c r="T10" s="8">
-        <v>1000</v>
-      </c>
       <c r="U10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V10" s="8">
         <v>1400</v>
       </c>
-      <c r="V10" s="8">
-        <v>1000</v>
-      </c>
       <c r="W10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X10" s="8">
         <v>1400</v>
       </c>
-      <c r="X10" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z10" s="8">
         <v>1400</v>
       </c>
-      <c r="Z10" s="8">
+      <c r="AA10" s="8">
         <v>1500</v>
       </c>
-      <c r="AA10" s="8">
+      <c r="AB10" s="8">
         <v>3000</v>
       </c>
-      <c r="AB10" s="8">
+      <c r="AC10" s="8">
         <v>0.95</v>
       </c>
-      <c r="AC10" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AD10" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AE10" s="8">
         <v>5000</v>
       </c>
-      <c r="AE10" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF10" s="8">
         <v>1000</v>
       </c>
       <c r="AG10" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH10" s="8">
         <v>350</v>
       </c>
       <c r="AI10" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ10" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ10" s="8">
-        <v>0</v>
-      </c>
       <c r="AK10" s="8">
         <v>0</v>
       </c>
       <c r="AL10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM10" s="8">
-        <v>0</v>
-      </c>
       <c r="AN10" s="8">
         <v>0</v>
       </c>
@@ -4610,178 +4157,181 @@
         <v>0</v>
       </c>
       <c r="AP10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="8">
         <v>6</v>
       </c>
-      <c r="AQ10" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR10" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS10" s="8">
         <v>6</v>
       </c>
-      <c r="AS10" s="8">
+      <c r="AT10" s="8">
         <v>132</v>
-      </c>
-      <c r="AT10" s="8">
-        <v>25</v>
       </c>
       <c r="AU10" s="8">
         <v>25</v>
       </c>
       <c r="AV10" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW10" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX10" s="12">
+      <c r="AX10" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY10" s="12">
         <v>3</v>
       </c>
-      <c r="AY10" s="8">
+      <c r="AZ10" s="8">
         <v>15</v>
       </c>
-      <c r="AZ10" s="12">
+      <c r="BA10" s="12">
         <v>10</v>
       </c>
-      <c r="BA10" s="8">
+      <c r="BB10" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB10" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC10" s="8" t="s">
+      <c r="BC10" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD10" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BD10" s="8">
-        <v>0</v>
-      </c>
       <c r="BE10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF10" s="18" t="s">
+      <c r="BG10" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="BG10" s="14" t="s">
+      <c r="BH10" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="BH10" s="15" t="s">
+      <c r="BI10" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="BI10" s="15" t="s">
+      <c r="BJ10" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:61">
+    <row r="11" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C11" s="7">
         <v>1000601</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E11" s="7">
-        <v>1000601</v>
+      <c r="E11" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="F11" s="7">
         <v>1000601</v>
       </c>
       <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="s">
+        <v>1000601</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
       <c r="J11" s="8">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="7">
         <v>2</v>
       </c>
-      <c r="L11" s="7">
-        <v>1</v>
-      </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="7">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N11" s="7">
-        <v>0</v>
-      </c>
       <c r="O11" s="7">
-        <v>1</v>
-      </c>
-      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8">
         <v>1500</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="R11" s="8">
         <v>3000</v>
       </c>
-      <c r="R11" s="8">
-        <v>1000</v>
-      </c>
       <c r="S11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T11" s="8">
         <v>1400</v>
       </c>
-      <c r="T11" s="8">
-        <v>1000</v>
-      </c>
       <c r="U11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V11" s="8">
         <v>1400</v>
       </c>
-      <c r="V11" s="8">
-        <v>1000</v>
-      </c>
       <c r="W11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X11" s="8">
         <v>1400</v>
       </c>
-      <c r="X11" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z11" s="8">
         <v>1400</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="AA11" s="8">
         <v>1500</v>
       </c>
-      <c r="AA11" s="8">
+      <c r="AB11" s="8">
         <v>3000</v>
       </c>
-      <c r="AB11" s="8">
+      <c r="AC11" s="8">
         <v>0.95</v>
       </c>
-      <c r="AC11" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AD11" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AE11" s="8">
         <v>5000</v>
       </c>
-      <c r="AE11" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF11" s="8">
         <v>1000</v>
       </c>
       <c r="AG11" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH11" s="8">
         <v>350</v>
       </c>
       <c r="AI11" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ11" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ11" s="8">
-        <v>0</v>
-      </c>
       <c r="AK11" s="8">
         <v>0</v>
       </c>
       <c r="AL11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM11" s="8">
-        <v>0</v>
-      </c>
       <c r="AN11" s="8">
         <v>0</v>
       </c>
@@ -4789,178 +4339,181 @@
         <v>0</v>
       </c>
       <c r="AP11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="8">
         <v>6</v>
       </c>
-      <c r="AQ11" s="8">
+      <c r="AR11" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR11" s="8">
+      <c r="AS11" s="8">
         <v>2</v>
       </c>
-      <c r="AS11" s="8">
+      <c r="AT11" s="8">
         <v>132</v>
-      </c>
-      <c r="AT11" s="8">
-        <v>25</v>
       </c>
       <c r="AU11" s="8">
         <v>25</v>
       </c>
       <c r="AV11" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW11" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX11" s="12">
+      <c r="AX11" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY11" s="12">
         <v>3</v>
       </c>
-      <c r="AY11" s="8">
+      <c r="AZ11" s="8">
         <v>15</v>
       </c>
-      <c r="AZ11" s="12">
+      <c r="BA11" s="12">
         <v>10</v>
       </c>
-      <c r="BA11" s="8">
+      <c r="BB11" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB11" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC11" s="8" t="s">
+      <c r="BC11" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BD11" s="8">
-        <v>0</v>
-      </c>
       <c r="BE11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF11" s="8">
+      <c r="BG11" s="8">
         <v>80001006</v>
       </c>
-      <c r="BG11" s="14" t="s">
+      <c r="BH11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="BH11" s="15" t="s">
+      <c r="BI11" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="BI11" s="15" t="s">
+      <c r="BJ11" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:61">
+    <row r="12" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C12" s="7">
         <v>1000701</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E12" s="7">
-        <v>1000701</v>
+      <c r="E12" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="F12" s="7">
         <v>1000701</v>
       </c>
       <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8" t="s">
+        <v>1000701</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="8">
-        <v>0</v>
-      </c>
       <c r="J12" s="8">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7">
         <v>2</v>
       </c>
-      <c r="L12" s="7">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="7">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N12" s="7">
-        <v>0</v>
-      </c>
       <c r="O12" s="7">
-        <v>1</v>
-      </c>
-      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="8">
         <v>1500</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="R12" s="8">
         <v>3000</v>
       </c>
-      <c r="R12" s="8">
-        <v>1000</v>
-      </c>
       <c r="S12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T12" s="8">
         <v>1500</v>
       </c>
-      <c r="T12" s="8">
-        <v>1000</v>
-      </c>
       <c r="U12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V12" s="8">
         <v>1500</v>
       </c>
-      <c r="V12" s="8">
-        <v>1000</v>
-      </c>
       <c r="W12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X12" s="8">
         <v>1300</v>
       </c>
-      <c r="X12" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z12" s="8">
         <v>1300</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="AA12" s="8">
         <v>1500</v>
       </c>
-      <c r="AA12" s="8">
+      <c r="AB12" s="8">
         <v>3000</v>
       </c>
-      <c r="AB12" s="8">
-        <v>1</v>
-      </c>
       <c r="AC12" s="8">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AD12" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AE12" s="8">
         <v>5000</v>
       </c>
-      <c r="AE12" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF12" s="8">
         <v>1000</v>
       </c>
       <c r="AG12" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH12" s="8">
         <v>350</v>
       </c>
       <c r="AI12" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ12" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ12" s="8">
-        <v>0</v>
-      </c>
       <c r="AK12" s="8">
         <v>0</v>
       </c>
       <c r="AL12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM12" s="8">
-        <v>0</v>
-      </c>
       <c r="AN12" s="8">
         <v>0</v>
       </c>
@@ -4968,178 +4521,181 @@
         <v>0</v>
       </c>
       <c r="AP12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="8">
         <v>6</v>
       </c>
-      <c r="AQ12" s="8">
+      <c r="AR12" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR12" s="8">
+      <c r="AS12" s="8">
         <v>2</v>
       </c>
-      <c r="AS12" s="8">
+      <c r="AT12" s="8">
         <v>132</v>
-      </c>
-      <c r="AT12" s="8">
-        <v>25</v>
       </c>
       <c r="AU12" s="8">
         <v>25</v>
       </c>
       <c r="AV12" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW12" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX12" s="12">
+      <c r="AX12" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY12" s="12">
         <v>3</v>
       </c>
-      <c r="AY12" s="8">
+      <c r="AZ12" s="8">
         <v>15</v>
       </c>
-      <c r="AZ12" s="12">
+      <c r="BA12" s="12">
         <v>10</v>
       </c>
-      <c r="BA12" s="8">
+      <c r="BB12" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB12" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC12" s="8" t="s">
+      <c r="BC12" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BD12" s="8">
-        <v>0</v>
-      </c>
       <c r="BE12" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF12" s="8">
+      <c r="BG12" s="8">
         <v>80001007</v>
       </c>
-      <c r="BG12" s="14" t="s">
+      <c r="BH12" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="BH12" s="15" t="s">
+      <c r="BI12" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="BI12" s="15" t="s">
+      <c r="BJ12" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:61">
+    <row r="13" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C13" s="7">
         <v>1000801</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="7">
-        <v>1000801</v>
+      <c r="E13" s="7" t="s">
+        <v>195</v>
       </c>
       <c r="F13" s="7">
         <v>1000801</v>
       </c>
       <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="s">
+        <v>1000801</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
       <c r="J13" s="8">
-        <v>1</v>
-      </c>
-      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="7">
         <v>2</v>
       </c>
-      <c r="L13" s="7">
-        <v>1</v>
-      </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="7">
+        <v>1</v>
+      </c>
+      <c r="N13" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N13" s="7">
-        <v>0</v>
-      </c>
       <c r="O13" s="7">
-        <v>1</v>
-      </c>
-      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8">
         <v>1500</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="R13" s="8">
         <v>3000</v>
       </c>
-      <c r="R13" s="8">
-        <v>1000</v>
-      </c>
       <c r="S13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="8">
         <v>1350</v>
       </c>
-      <c r="T13" s="8">
-        <v>1000</v>
-      </c>
       <c r="U13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V13" s="8">
         <v>1350</v>
       </c>
-      <c r="V13" s="8">
-        <v>1000</v>
-      </c>
       <c r="W13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X13" s="8">
         <v>1500</v>
       </c>
-      <c r="X13" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y13" s="8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z13" s="8">
         <v>1500</v>
       </c>
       <c r="AA13" s="8">
+        <v>1500</v>
+      </c>
+      <c r="AB13" s="8">
         <v>3000</v>
       </c>
-      <c r="AB13" s="8">
-        <v>1</v>
-      </c>
       <c r="AC13" s="8">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AE13" s="8">
         <v>5000</v>
       </c>
-      <c r="AE13" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF13" s="8">
         <v>1000</v>
       </c>
       <c r="AG13" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH13" s="8">
         <v>350</v>
       </c>
       <c r="AI13" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ13" s="8">
-        <v>0</v>
-      </c>
       <c r="AK13" s="8">
         <v>0</v>
       </c>
       <c r="AL13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM13" s="8">
-        <v>0</v>
-      </c>
       <c r="AN13" s="8">
         <v>0</v>
       </c>
@@ -5147,178 +4703,181 @@
         <v>0</v>
       </c>
       <c r="AP13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="8">
         <v>6</v>
       </c>
-      <c r="AQ13" s="8">
+      <c r="AR13" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR13" s="8">
+      <c r="AS13" s="8">
         <v>2</v>
       </c>
-      <c r="AS13" s="8">
+      <c r="AT13" s="8">
         <v>132</v>
-      </c>
-      <c r="AT13" s="8">
-        <v>25</v>
       </c>
       <c r="AU13" s="8">
         <v>25</v>
       </c>
       <c r="AV13" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW13" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX13" s="12">
+      <c r="AX13" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY13" s="12">
         <v>3</v>
       </c>
-      <c r="AY13" s="8">
+      <c r="AZ13" s="8">
         <v>15</v>
       </c>
-      <c r="AZ13" s="12">
+      <c r="BA13" s="12">
         <v>10</v>
       </c>
-      <c r="BA13" s="8">
+      <c r="BB13" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB13" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC13" s="8" t="s">
+      <c r="BC13" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BD13" s="8">
-        <v>0</v>
-      </c>
       <c r="BE13" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF13" s="8" t="s">
+      <c r="BG13" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="BG13" s="14" t="s">
+      <c r="BH13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="BH13" s="15" t="s">
+      <c r="BI13" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="BI13" s="15" t="s">
+      <c r="BJ13" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:61">
+    <row r="14" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C14" s="7">
         <v>1000901</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E14" s="7">
-        <v>1000901</v>
+      <c r="E14" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="F14" s="7">
         <v>1000901</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="s">
+        <v>1000901</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
       <c r="J14" s="8">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7">
         <v>2</v>
       </c>
-      <c r="L14" s="7">
-        <v>1</v>
-      </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="7">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N14" s="7">
-        <v>0</v>
-      </c>
       <c r="O14" s="7">
-        <v>1</v>
-      </c>
-      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="8">
         <v>1500</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="R14" s="8">
         <v>2500</v>
       </c>
-      <c r="R14" s="8">
-        <v>1000</v>
-      </c>
       <c r="S14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T14" s="8">
         <v>1500</v>
       </c>
-      <c r="T14" s="8">
-        <v>1000</v>
-      </c>
       <c r="U14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V14" s="8">
         <v>1400</v>
       </c>
-      <c r="V14" s="8">
-        <v>1000</v>
-      </c>
       <c r="W14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X14" s="8">
         <v>1400</v>
       </c>
-      <c r="X14" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z14" s="8">
         <v>1400</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="AA14" s="8">
         <v>1500</v>
       </c>
-      <c r="AA14" s="8">
+      <c r="AB14" s="8">
         <v>3000</v>
       </c>
-      <c r="AB14" s="8">
-        <v>1</v>
-      </c>
       <c r="AC14" s="8">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AD14" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AE14" s="8">
         <v>5000</v>
       </c>
-      <c r="AE14" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF14" s="8">
         <v>1000</v>
       </c>
       <c r="AG14" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH14" s="8">
         <v>350</v>
       </c>
       <c r="AI14" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ14" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ14" s="8">
-        <v>0</v>
-      </c>
       <c r="AK14" s="8">
         <v>0</v>
       </c>
       <c r="AL14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM14" s="8">
-        <v>0</v>
-      </c>
       <c r="AN14" s="8">
         <v>0</v>
       </c>
@@ -5326,178 +4885,181 @@
         <v>0</v>
       </c>
       <c r="AP14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="8">
         <v>6</v>
       </c>
-      <c r="AQ14" s="8">
+      <c r="AR14" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR14" s="8">
+      <c r="AS14" s="8">
         <v>2</v>
       </c>
-      <c r="AS14" s="8">
+      <c r="AT14" s="8">
         <v>132</v>
-      </c>
-      <c r="AT14" s="8">
-        <v>25</v>
       </c>
       <c r="AU14" s="8">
         <v>25</v>
       </c>
       <c r="AV14" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW14" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX14" s="12">
+      <c r="AX14" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY14" s="12">
         <v>3</v>
       </c>
-      <c r="AY14" s="8">
+      <c r="AZ14" s="8">
         <v>15</v>
       </c>
-      <c r="AZ14" s="12">
+      <c r="BA14" s="12">
         <v>10</v>
       </c>
-      <c r="BA14" s="8">
+      <c r="BB14" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB14" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC14" s="8" t="s">
+      <c r="BC14" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BD14" s="8">
-        <v>0</v>
-      </c>
       <c r="BE14" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF14" s="8">
+      <c r="BG14" s="8">
         <v>80001009</v>
       </c>
-      <c r="BG14" s="14" t="s">
+      <c r="BH14" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="BH14" s="15" t="s">
+      <c r="BI14" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="BI14" s="15" t="s">
+      <c r="BJ14" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:61">
+    <row r="15" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C15" s="7">
         <v>1001001</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="7">
-        <v>1001001</v>
+      <c r="E15" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="F15" s="7">
         <v>1001001</v>
       </c>
       <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8" t="s">
+        <v>1001001</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
       <c r="J15" s="8">
-        <v>1</v>
-      </c>
-      <c r="K15" s="7">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="7">
         <v>3</v>
       </c>
-      <c r="L15" s="7">
-        <v>1</v>
-      </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="7">
+        <v>1</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N15" s="7">
-        <v>0</v>
-      </c>
       <c r="O15" s="7">
-        <v>1</v>
-      </c>
-      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="8">
         <v>1500</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="R15" s="8">
         <v>3000</v>
       </c>
-      <c r="R15" s="8">
-        <v>1000</v>
-      </c>
       <c r="S15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T15" s="8">
         <v>1500</v>
       </c>
-      <c r="T15" s="8">
-        <v>1000</v>
-      </c>
       <c r="U15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V15" s="8">
         <v>1500</v>
       </c>
-      <c r="V15" s="8">
-        <v>1000</v>
-      </c>
       <c r="W15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X15" s="8">
         <v>1400</v>
       </c>
-      <c r="X15" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z15" s="8">
         <v>1400</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="AA15" s="8">
         <v>1500</v>
       </c>
-      <c r="AA15" s="8">
+      <c r="AB15" s="8">
         <v>3000</v>
       </c>
-      <c r="AB15" s="8">
-        <v>1</v>
-      </c>
       <c r="AC15" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="8">
         <v>1.2</v>
       </c>
-      <c r="AD15" s="8">
+      <c r="AE15" s="8">
         <v>5000</v>
       </c>
-      <c r="AE15" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF15" s="8">
         <v>1000</v>
       </c>
       <c r="AG15" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH15" s="8">
         <v>350</v>
       </c>
       <c r="AI15" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ15" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ15" s="8">
-        <v>0</v>
-      </c>
       <c r="AK15" s="8">
         <v>0</v>
       </c>
       <c r="AL15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM15" s="8">
-        <v>0</v>
-      </c>
       <c r="AN15" s="8">
         <v>0</v>
       </c>
@@ -5505,178 +5067,181 @@
         <v>0</v>
       </c>
       <c r="AP15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="8">
         <v>6</v>
       </c>
-      <c r="AQ15" s="8">
+      <c r="AR15" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR15" s="8">
+      <c r="AS15" s="8">
         <v>2</v>
       </c>
-      <c r="AS15" s="8">
+      <c r="AT15" s="8">
         <v>132</v>
-      </c>
-      <c r="AT15" s="8">
-        <v>25</v>
       </c>
       <c r="AU15" s="8">
         <v>25</v>
       </c>
       <c r="AV15" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW15" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX15" s="12">
+      <c r="AX15" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY15" s="12">
         <v>3</v>
       </c>
-      <c r="AY15" s="8">
+      <c r="AZ15" s="8">
         <v>15</v>
       </c>
-      <c r="AZ15" s="12">
+      <c r="BA15" s="12">
         <v>10</v>
       </c>
-      <c r="BA15" s="8">
+      <c r="BB15" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB15" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC15" s="8" t="s">
+      <c r="BC15" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD15" s="8">
-        <v>0</v>
-      </c>
       <c r="BE15" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF15" s="8" t="s">
+      <c r="BG15" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="BG15" s="14" t="s">
+      <c r="BH15" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="BH15" s="15" t="s">
+      <c r="BI15" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="BI15" s="15" t="s">
+      <c r="BJ15" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:61">
+    <row r="16" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C16" s="7">
         <v>1001101</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="7">
-        <v>1001101</v>
+      <c r="E16" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="F16" s="7">
         <v>1001101</v>
       </c>
       <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="s">
+        <v>1001101</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="8">
-        <v>0</v>
-      </c>
       <c r="J16" s="8">
-        <v>1</v>
-      </c>
-      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1</v>
+      </c>
+      <c r="L16" s="7">
         <v>3</v>
       </c>
-      <c r="L16" s="7">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="7">
+        <v>1</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N16" s="7">
-        <v>0</v>
-      </c>
       <c r="O16" s="7">
-        <v>1</v>
-      </c>
-      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="8">
         <v>1500</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="R16" s="8">
         <v>2500</v>
       </c>
-      <c r="R16" s="8">
-        <v>1000</v>
-      </c>
       <c r="S16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T16" s="8">
         <v>1500</v>
       </c>
-      <c r="T16" s="8">
-        <v>1000</v>
-      </c>
       <c r="U16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V16" s="8">
         <v>1500</v>
       </c>
-      <c r="V16" s="8">
-        <v>1000</v>
-      </c>
       <c r="W16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X16" s="8">
         <v>1300</v>
       </c>
-      <c r="X16" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z16" s="8">
         <v>1300</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="AA16" s="8">
         <v>1500</v>
       </c>
-      <c r="AA16" s="8">
+      <c r="AB16" s="8">
         <v>3000</v>
       </c>
-      <c r="AB16" s="8">
-        <v>1</v>
-      </c>
       <c r="AC16" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="8">
         <v>1.2</v>
       </c>
-      <c r="AD16" s="8">
+      <c r="AE16" s="8">
         <v>5000</v>
       </c>
-      <c r="AE16" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF16" s="8">
         <v>1000</v>
       </c>
       <c r="AG16" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH16" s="8">
         <v>350</v>
       </c>
       <c r="AI16" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ16" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ16" s="8">
-        <v>0</v>
-      </c>
       <c r="AK16" s="8">
         <v>0</v>
       </c>
       <c r="AL16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM16" s="8">
-        <v>0</v>
-      </c>
       <c r="AN16" s="8">
         <v>0</v>
       </c>
@@ -5684,178 +5249,181 @@
         <v>0</v>
       </c>
       <c r="AP16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="8">
         <v>6</v>
       </c>
-      <c r="AQ16" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR16" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS16" s="8">
         <v>6</v>
       </c>
-      <c r="AS16" s="8">
+      <c r="AT16" s="8">
         <v>132</v>
-      </c>
-      <c r="AT16" s="8">
-        <v>25</v>
       </c>
       <c r="AU16" s="8">
         <v>25</v>
       </c>
       <c r="AV16" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW16" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX16" s="12">
+      <c r="AX16" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY16" s="12">
         <v>3</v>
       </c>
-      <c r="AY16" s="8">
+      <c r="AZ16" s="8">
         <v>15</v>
       </c>
-      <c r="AZ16" s="12">
+      <c r="BA16" s="12">
         <v>10</v>
       </c>
-      <c r="BA16" s="8">
+      <c r="BB16" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB16" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC16" s="8" t="s">
+      <c r="BC16" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD16" s="8">
-        <v>0</v>
-      </c>
       <c r="BE16" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF16" s="8" t="s">
+      <c r="BG16" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="BG16" s="14" t="s">
+      <c r="BH16" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="BH16" s="15" t="s">
+      <c r="BI16" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="BI16" s="15" t="s">
+      <c r="BJ16" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:61">
+    <row r="17" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C17" s="7">
         <v>1001201</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="7">
-        <v>1001201</v>
+      <c r="E17" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="F17" s="7">
         <v>1001201</v>
       </c>
       <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="s">
+        <v>1001201</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="8">
-        <v>0</v>
-      </c>
       <c r="J17" s="8">
-        <v>1</v>
-      </c>
-      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7">
         <v>3</v>
       </c>
-      <c r="L17" s="7">
-        <v>1</v>
-      </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" s="7">
+        <v>1</v>
+      </c>
+      <c r="N17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N17" s="7">
-        <v>0</v>
-      </c>
       <c r="O17" s="7">
-        <v>1</v>
-      </c>
-      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="8">
         <v>1500</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="R17" s="8">
         <v>2500</v>
       </c>
-      <c r="R17" s="8">
-        <v>1000</v>
-      </c>
       <c r="S17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T17" s="8">
         <v>1500</v>
       </c>
-      <c r="T17" s="8">
-        <v>1000</v>
-      </c>
       <c r="U17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V17" s="8">
         <v>1500</v>
       </c>
-      <c r="V17" s="8">
-        <v>1000</v>
-      </c>
       <c r="W17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X17" s="8">
         <v>1300</v>
       </c>
-      <c r="X17" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z17" s="8">
         <v>1300</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="AA17" s="8">
         <v>1500</v>
       </c>
-      <c r="AA17" s="8">
+      <c r="AB17" s="8">
         <v>3000</v>
       </c>
-      <c r="AB17" s="8">
-        <v>1</v>
-      </c>
       <c r="AC17" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD17" s="8">
+      <c r="AE17" s="8">
         <v>5000</v>
       </c>
-      <c r="AE17" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF17" s="8">
         <v>1000</v>
       </c>
       <c r="AG17" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH17" s="8">
         <v>350</v>
       </c>
       <c r="AI17" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ17" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ17" s="8">
-        <v>0</v>
-      </c>
       <c r="AK17" s="8">
         <v>0</v>
       </c>
       <c r="AL17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM17" s="8">
-        <v>0</v>
-      </c>
       <c r="AN17" s="8">
         <v>0</v>
       </c>
@@ -5863,178 +5431,181 @@
         <v>0</v>
       </c>
       <c r="AP17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="8">
         <v>6</v>
       </c>
-      <c r="AQ17" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR17" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS17" s="8">
         <v>6</v>
       </c>
-      <c r="AS17" s="8">
+      <c r="AT17" s="8">
         <v>132</v>
-      </c>
-      <c r="AT17" s="8">
-        <v>25</v>
       </c>
       <c r="AU17" s="8">
         <v>25</v>
       </c>
       <c r="AV17" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW17" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX17" s="12">
+      <c r="AX17" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY17" s="12">
         <v>3</v>
       </c>
-      <c r="AY17" s="8">
+      <c r="AZ17" s="8">
         <v>15</v>
       </c>
-      <c r="AZ17" s="12">
+      <c r="BA17" s="12">
         <v>10</v>
       </c>
-      <c r="BA17" s="8">
+      <c r="BB17" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB17" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC17" s="8" t="s">
+      <c r="BC17" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD17" s="8">
-        <v>0</v>
-      </c>
       <c r="BE17" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF17" s="8" t="s">
+      <c r="BG17" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="BG17" s="14" t="s">
+      <c r="BH17" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="BH17" s="15" t="s">
+      <c r="BI17" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="BI17" s="15" t="s">
+      <c r="BJ17" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:61">
+    <row r="18" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C18" s="7">
         <v>1001301</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="7">
-        <v>1001301</v>
+      <c r="E18" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="F18" s="7">
         <v>1001301</v>
       </c>
       <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8" t="s">
+        <v>1001301</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="8">
-        <v>0</v>
-      </c>
       <c r="J18" s="8">
-        <v>1</v>
-      </c>
-      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7">
         <v>3</v>
       </c>
-      <c r="L18" s="7">
-        <v>1</v>
-      </c>
-      <c r="M18" s="7" t="s">
+      <c r="M18" s="7">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N18" s="7">
-        <v>0</v>
-      </c>
       <c r="O18" s="7">
-        <v>1</v>
-      </c>
-      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="8">
         <v>1500</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="R18" s="8">
         <v>2750</v>
       </c>
-      <c r="R18" s="8">
-        <v>1000</v>
-      </c>
       <c r="S18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T18" s="8">
         <v>1500</v>
       </c>
-      <c r="T18" s="8">
-        <v>1000</v>
-      </c>
       <c r="U18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V18" s="8">
         <v>1500</v>
       </c>
-      <c r="V18" s="8">
-        <v>1000</v>
-      </c>
       <c r="W18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X18" s="8">
         <v>1300</v>
       </c>
-      <c r="X18" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z18" s="8">
         <v>1300</v>
       </c>
-      <c r="Z18" s="8">
+      <c r="AA18" s="8">
         <v>1500</v>
       </c>
-      <c r="AA18" s="8">
+      <c r="AB18" s="8">
         <v>3000</v>
       </c>
-      <c r="AB18" s="8">
-        <v>1</v>
-      </c>
       <c r="AC18" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD18" s="8">
+      <c r="AE18" s="8">
         <v>5000</v>
       </c>
-      <c r="AE18" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF18" s="8">
         <v>1000</v>
       </c>
       <c r="AG18" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH18" s="8">
         <v>350</v>
       </c>
       <c r="AI18" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ18" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ18" s="8">
-        <v>0</v>
-      </c>
       <c r="AK18" s="8">
         <v>0</v>
       </c>
       <c r="AL18" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM18" s="8">
-        <v>0</v>
-      </c>
       <c r="AN18" s="8">
         <v>0</v>
       </c>
@@ -6042,178 +5613,181 @@
         <v>0</v>
       </c>
       <c r="AP18" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="8">
         <v>6</v>
       </c>
-      <c r="AQ18" s="8">
+      <c r="AR18" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR18" s="8">
+      <c r="AS18" s="8">
         <v>2</v>
       </c>
-      <c r="AS18" s="8">
+      <c r="AT18" s="8">
         <v>132</v>
-      </c>
-      <c r="AT18" s="8">
-        <v>25</v>
       </c>
       <c r="AU18" s="8">
         <v>25</v>
       </c>
       <c r="AV18" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW18" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX18" s="12">
+      <c r="AX18" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY18" s="12">
         <v>3</v>
       </c>
-      <c r="AY18" s="8">
+      <c r="AZ18" s="8">
         <v>15</v>
       </c>
-      <c r="AZ18" s="12">
+      <c r="BA18" s="12">
         <v>10</v>
       </c>
-      <c r="BA18" s="8">
+      <c r="BB18" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB18" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC18" s="8" t="s">
+      <c r="BC18" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD18" s="8">
-        <v>0</v>
-      </c>
       <c r="BE18" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF18" s="8" t="s">
+      <c r="BG18" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="BG18" s="14" t="s">
+      <c r="BH18" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="BH18" s="15" t="s">
+      <c r="BI18" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BI18" s="15" t="s">
+      <c r="BJ18" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:61">
+    <row r="19" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C19" s="7">
         <v>1001401</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="7">
-        <v>1001401</v>
+      <c r="E19" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="F19" s="7">
         <v>1001401</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="s">
+        <v>1001401</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
       <c r="J19" s="8">
-        <v>1</v>
-      </c>
-      <c r="K19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7">
         <v>3</v>
       </c>
-      <c r="L19" s="7">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7" t="s">
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N19" s="7">
-        <v>0</v>
-      </c>
       <c r="O19" s="7">
-        <v>1</v>
-      </c>
-      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="8">
         <v>1500</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="R19" s="8">
         <v>3000</v>
       </c>
-      <c r="R19" s="8">
-        <v>1000</v>
-      </c>
       <c r="S19" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T19" s="8">
         <v>1500</v>
       </c>
-      <c r="T19" s="8">
-        <v>1000</v>
-      </c>
       <c r="U19" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V19" s="8">
         <v>1500</v>
       </c>
-      <c r="V19" s="8">
-        <v>1000</v>
-      </c>
       <c r="W19" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X19" s="8">
         <v>1500</v>
       </c>
-      <c r="X19" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y19" s="8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z19" s="8">
         <v>1500</v>
       </c>
       <c r="AA19" s="8">
+        <v>1500</v>
+      </c>
+      <c r="AB19" s="8">
         <v>3000</v>
       </c>
-      <c r="AB19" s="8">
-        <v>1</v>
-      </c>
       <c r="AC19" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD19" s="8">
+      <c r="AE19" s="8">
         <v>5000</v>
       </c>
-      <c r="AE19" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF19" s="8">
         <v>1000</v>
       </c>
       <c r="AG19" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH19" s="8">
         <v>350</v>
       </c>
       <c r="AI19" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ19" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ19" s="8">
-        <v>0</v>
-      </c>
       <c r="AK19" s="8">
         <v>0</v>
       </c>
       <c r="AL19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM19" s="8">
-        <v>0</v>
-      </c>
       <c r="AN19" s="8">
         <v>0</v>
       </c>
@@ -6221,178 +5795,181 @@
         <v>0</v>
       </c>
       <c r="AP19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="8">
         <v>6</v>
       </c>
-      <c r="AQ19" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS19" s="8">
         <v>6</v>
       </c>
-      <c r="AS19" s="8">
+      <c r="AT19" s="8">
         <v>132</v>
-      </c>
-      <c r="AT19" s="8">
-        <v>25</v>
       </c>
       <c r="AU19" s="8">
         <v>25</v>
       </c>
       <c r="AV19" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW19" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX19" s="12">
+      <c r="AX19" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY19" s="12">
         <v>3</v>
       </c>
-      <c r="AY19" s="8">
+      <c r="AZ19" s="8">
         <v>15</v>
       </c>
-      <c r="AZ19" s="12">
+      <c r="BA19" s="12">
         <v>10</v>
       </c>
-      <c r="BA19" s="8">
+      <c r="BB19" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB19" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC19" s="8" t="s">
+      <c r="BC19" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD19" s="8">
-        <v>0</v>
-      </c>
       <c r="BE19" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF19" s="8" t="s">
+      <c r="BG19" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="BG19" s="14" t="s">
+      <c r="BH19" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="BH19" s="15" t="s">
+      <c r="BI19" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="BI19" s="15" t="s">
+      <c r="BJ19" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:61">
+    <row r="20" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C20" s="7">
         <v>1009101</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="7">
-        <v>1009101</v>
+      <c r="E20" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="F20" s="7">
         <v>1009101</v>
       </c>
       <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8" t="s">
+        <v>1009101</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I20" s="8">
-        <v>0</v>
-      </c>
       <c r="J20" s="8">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7">
         <v>4</v>
       </c>
-      <c r="L20" s="7">
-        <v>1</v>
-      </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="7">
+        <v>1</v>
+      </c>
+      <c r="N20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="7">
-        <v>0</v>
-      </c>
       <c r="O20" s="7">
-        <v>1</v>
-      </c>
-      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="8">
         <v>1500</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="R20" s="8">
         <v>2750</v>
       </c>
-      <c r="R20" s="8">
-        <v>1000</v>
-      </c>
       <c r="S20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T20" s="8">
         <v>1500</v>
       </c>
-      <c r="T20" s="8">
-        <v>1000</v>
-      </c>
       <c r="U20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V20" s="8">
         <v>1500</v>
       </c>
-      <c r="V20" s="8">
-        <v>1000</v>
-      </c>
       <c r="W20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X20" s="8">
         <v>1300</v>
       </c>
-      <c r="X20" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="8">
         <v>1300</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="AA20" s="8">
         <v>1500</v>
       </c>
-      <c r="AA20" s="8">
+      <c r="AB20" s="8">
         <v>3000</v>
       </c>
-      <c r="AB20" s="8">
-        <v>1</v>
-      </c>
       <c r="AC20" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD20" s="8">
+      <c r="AE20" s="8">
         <v>5000</v>
       </c>
-      <c r="AE20" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF20" s="8">
         <v>1000</v>
       </c>
       <c r="AG20" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH20" s="8">
         <v>350</v>
       </c>
       <c r="AI20" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ20" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ20" s="8">
-        <v>0</v>
-      </c>
       <c r="AK20" s="8">
         <v>0</v>
       </c>
       <c r="AL20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM20" s="8">
-        <v>0</v>
-      </c>
       <c r="AN20" s="8">
         <v>0</v>
       </c>
@@ -6400,178 +5977,181 @@
         <v>0</v>
       </c>
       <c r="AP20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="8">
         <v>6</v>
       </c>
-      <c r="AQ20" s="8">
+      <c r="AR20" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR20" s="8">
+      <c r="AS20" s="8">
         <v>2</v>
       </c>
-      <c r="AS20" s="8">
+      <c r="AT20" s="8">
         <v>132</v>
-      </c>
-      <c r="AT20" s="8">
-        <v>25</v>
       </c>
       <c r="AU20" s="8">
         <v>25</v>
       </c>
       <c r="AV20" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW20" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX20" s="12">
+      <c r="AX20" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY20" s="12">
         <v>3</v>
       </c>
-      <c r="AY20" s="8">
+      <c r="AZ20" s="8">
         <v>15</v>
       </c>
-      <c r="AZ20" s="12">
+      <c r="BA20" s="12">
         <v>10</v>
       </c>
-      <c r="BA20" s="8">
+      <c r="BB20" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB20" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC20" s="8" t="s">
+      <c r="BC20" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD20" s="8">
-        <v>0</v>
-      </c>
       <c r="BE20" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF20" s="8" t="s">
+      <c r="BG20" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="BG20" s="14" t="s">
+      <c r="BH20" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="BH20" s="15" t="s">
+      <c r="BI20" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="BI20" s="15" t="s">
+      <c r="BJ20" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:61">
+    <row r="21" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C21" s="7">
         <v>1009201</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E21" s="7">
-        <v>1009201</v>
+      <c r="E21" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="F21" s="7">
         <v>1009201</v>
       </c>
       <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="s">
+        <v>1009201</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I21" s="8">
-        <v>0</v>
-      </c>
       <c r="J21" s="8">
-        <v>1</v>
-      </c>
-      <c r="K21" s="7">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7">
         <v>4</v>
       </c>
-      <c r="L21" s="7">
-        <v>1</v>
-      </c>
-      <c r="M21" s="7" t="s">
+      <c r="M21" s="7">
+        <v>1</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N21" s="7">
-        <v>0</v>
-      </c>
       <c r="O21" s="7">
-        <v>1</v>
-      </c>
-      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="P21" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8">
         <v>1500</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="R21" s="8">
         <v>2750</v>
       </c>
-      <c r="R21" s="8">
-        <v>1000</v>
-      </c>
       <c r="S21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T21" s="8">
         <v>1500</v>
       </c>
-      <c r="T21" s="8">
-        <v>1000</v>
-      </c>
       <c r="U21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V21" s="8">
         <v>1500</v>
       </c>
-      <c r="V21" s="8">
-        <v>1000</v>
-      </c>
       <c r="W21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X21" s="8">
         <v>1300</v>
       </c>
-      <c r="X21" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="Z21" s="8">
         <v>1300</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="AA21" s="8">
         <v>1500</v>
       </c>
-      <c r="AA21" s="8">
+      <c r="AB21" s="8">
         <v>3000</v>
       </c>
-      <c r="AB21" s="8">
-        <v>1</v>
-      </c>
       <c r="AC21" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD21" s="8">
+      <c r="AE21" s="8">
         <v>5000</v>
       </c>
-      <c r="AE21" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF21" s="8">
         <v>1000</v>
       </c>
       <c r="AG21" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH21" s="8">
         <v>350</v>
       </c>
       <c r="AI21" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ21" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ21" s="8">
-        <v>0</v>
-      </c>
       <c r="AK21" s="8">
         <v>0</v>
       </c>
       <c r="AL21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM21" s="8">
-        <v>0</v>
-      </c>
       <c r="AN21" s="8">
         <v>0</v>
       </c>
@@ -6579,178 +6159,181 @@
         <v>0</v>
       </c>
       <c r="AP21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="8">
         <v>6</v>
       </c>
-      <c r="AQ21" s="8">
+      <c r="AR21" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR21" s="8">
+      <c r="AS21" s="8">
         <v>2</v>
       </c>
-      <c r="AS21" s="8">
+      <c r="AT21" s="8">
         <v>132</v>
-      </c>
-      <c r="AT21" s="8">
-        <v>25</v>
       </c>
       <c r="AU21" s="8">
         <v>25</v>
       </c>
       <c r="AV21" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW21" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX21" s="12">
+      <c r="AX21" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY21" s="12">
         <v>3</v>
       </c>
-      <c r="AY21" s="8">
+      <c r="AZ21" s="8">
         <v>15</v>
       </c>
-      <c r="AZ21" s="12">
+      <c r="BA21" s="12">
         <v>10</v>
       </c>
-      <c r="BA21" s="8">
+      <c r="BB21" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB21" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC21" s="8" t="s">
+      <c r="BC21" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD21" s="8">
-        <v>0</v>
-      </c>
       <c r="BE21" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF21" s="8" t="s">
+      <c r="BG21" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="BG21" s="14" t="s">
+      <c r="BH21" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="BH21" s="15" t="s">
+      <c r="BI21" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="BI21" s="15" t="s">
+      <c r="BJ21" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:61">
+    <row r="22" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C22" s="7">
         <v>1009301</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E22" s="7">
-        <v>1009301</v>
+      <c r="E22" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="F22" s="7">
         <v>1009301</v>
       </c>
       <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8" t="s">
+        <v>1009301</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I22" s="8">
-        <v>0</v>
-      </c>
       <c r="J22" s="8">
-        <v>1</v>
-      </c>
-      <c r="K22" s="7">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>1</v>
+      </c>
+      <c r="L22" s="7">
         <v>4</v>
       </c>
-      <c r="L22" s="7">
-        <v>1</v>
-      </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" s="7">
+        <v>1</v>
+      </c>
+      <c r="N22" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N22" s="7">
-        <v>0</v>
-      </c>
       <c r="O22" s="7">
-        <v>1</v>
-      </c>
-      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="8">
         <v>1500</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="R22" s="8">
         <v>3000</v>
       </c>
-      <c r="R22" s="8">
-        <v>1000</v>
-      </c>
       <c r="S22" s="8">
+        <v>1000</v>
+      </c>
+      <c r="T22" s="8">
         <v>1500</v>
       </c>
-      <c r="T22" s="8">
-        <v>1000</v>
-      </c>
       <c r="U22" s="8">
+        <v>1000</v>
+      </c>
+      <c r="V22" s="8">
         <v>1500</v>
       </c>
-      <c r="V22" s="8">
-        <v>1000</v>
-      </c>
       <c r="W22" s="8">
+        <v>1000</v>
+      </c>
+      <c r="X22" s="8">
         <v>1500</v>
       </c>
-      <c r="X22" s="8">
-        <v>1000</v>
-      </c>
       <c r="Y22" s="8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z22" s="8">
         <v>1500</v>
       </c>
       <c r="AA22" s="8">
+        <v>1500</v>
+      </c>
+      <c r="AB22" s="8">
         <v>3000</v>
       </c>
-      <c r="AB22" s="8">
-        <v>1</v>
-      </c>
       <c r="AC22" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="8">
         <v>1.25</v>
       </c>
-      <c r="AD22" s="8">
+      <c r="AE22" s="8">
         <v>5000</v>
       </c>
-      <c r="AE22" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF22" s="8">
         <v>1000</v>
       </c>
       <c r="AG22" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH22" s="8">
         <v>350</v>
       </c>
       <c r="AI22" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ22" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ22" s="8">
-        <v>0</v>
-      </c>
       <c r="AK22" s="8">
         <v>0</v>
       </c>
       <c r="AL22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM22" s="8">
-        <v>0</v>
-      </c>
       <c r="AN22" s="8">
         <v>0</v>
       </c>
@@ -6758,114 +6341,117 @@
         <v>0</v>
       </c>
       <c r="AP22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="8">
         <v>6</v>
       </c>
-      <c r="AQ22" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR22" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS22" s="8">
         <v>6</v>
       </c>
-      <c r="AS22" s="8">
+      <c r="AT22" s="8">
         <v>132</v>
-      </c>
-      <c r="AT22" s="8">
-        <v>25</v>
       </c>
       <c r="AU22" s="8">
         <v>25</v>
       </c>
       <c r="AV22" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW22" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX22" s="12">
+      <c r="AX22" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY22" s="12">
         <v>3</v>
       </c>
-      <c r="AY22" s="8">
+      <c r="AZ22" s="8">
         <v>15</v>
       </c>
-      <c r="AZ22" s="12">
+      <c r="BA22" s="12">
         <v>10</v>
       </c>
-      <c r="BA22" s="8">
+      <c r="BB22" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB22" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC22" s="8" t="s">
+      <c r="BC22" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BD22" s="8">
-        <v>0</v>
-      </c>
       <c r="BE22" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF22" s="8" t="s">
+      <c r="BG22" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="BG22" s="14" t="s">
+      <c r="BH22" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="BH22" s="15" t="s">
+      <c r="BI22" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="BI22" s="15" t="s">
+      <c r="BJ22" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:61">
+    <row r="23" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C23" s="7">
         <v>2000001</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E23" s="7">
-        <v>2000001</v>
+      <c r="E23" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="F23" s="7">
         <v>2000001</v>
       </c>
       <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8" t="s">
+        <v>2000001</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I23" s="8">
+      <c r="J23" s="8">
         <v>2</v>
       </c>
-      <c r="J23" s="8">
-        <v>1</v>
-      </c>
-      <c r="K23" s="7">
+      <c r="K23" s="8">
+        <v>1</v>
+      </c>
+      <c r="L23" s="7">
         <v>5</v>
       </c>
-      <c r="L23" s="7">
-        <v>1</v>
-      </c>
-      <c r="M23" s="7" t="s">
+      <c r="M23" s="7">
+        <v>1</v>
+      </c>
+      <c r="N23" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N23" s="7">
-        <v>0</v>
-      </c>
       <c r="O23" s="7">
-        <v>1</v>
-      </c>
-      <c r="P23" s="8">
-        <v>3200</v>
+        <v>0</v>
+      </c>
+      <c r="P23" s="7">
+        <v>1</v>
       </c>
       <c r="Q23" s="8">
         <v>3200</v>
       </c>
       <c r="R23" s="8">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="S23" s="8">
         <v>1600</v>
@@ -6889,47 +6475,47 @@
         <v>1600</v>
       </c>
       <c r="Z23" s="8">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="AA23" s="8">
         <v>3000</v>
       </c>
       <c r="AB23" s="8">
-        <v>1.5</v>
+        <v>3000</v>
       </c>
       <c r="AC23" s="8">
         <v>1.5</v>
       </c>
       <c r="AD23" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="AE23" s="8">
         <v>5000</v>
       </c>
-      <c r="AE23" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF23" s="8">
         <v>1000</v>
       </c>
       <c r="AG23" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH23" s="8">
         <v>350</v>
       </c>
       <c r="AI23" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ23" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ23" s="8">
-        <v>0</v>
-      </c>
       <c r="AK23" s="8">
         <v>0</v>
       </c>
       <c r="AL23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM23" s="8">
-        <v>0</v>
-      </c>
       <c r="AN23" s="8">
         <v>0</v>
       </c>
@@ -6937,112 +6523,115 @@
         <v>0</v>
       </c>
       <c r="AP23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="8">
         <v>6</v>
       </c>
-      <c r="AQ23" s="8">
+      <c r="AR23" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR23" s="8">
+      <c r="AS23" s="8">
         <v>2</v>
       </c>
-      <c r="AS23" s="8">
+      <c r="AT23" s="8">
         <v>132</v>
-      </c>
-      <c r="AT23" s="8">
-        <v>25</v>
       </c>
       <c r="AU23" s="8">
         <v>25</v>
       </c>
       <c r="AV23" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW23" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX23" s="12">
+      <c r="AX23" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY23" s="12">
         <v>3</v>
       </c>
-      <c r="AY23" s="8">
+      <c r="AZ23" s="8">
         <v>15</v>
       </c>
-      <c r="AZ23" s="12">
+      <c r="BA23" s="12">
         <v>10</v>
       </c>
-      <c r="BA23" s="8">
+      <c r="BB23" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB23" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC23" s="8"/>
-      <c r="BD23" s="8">
-        <v>0</v>
-      </c>
+      <c r="BC23" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="8"/>
       <c r="BE23" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF23" s="19" t="s">
+      <c r="BG23" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="BG23" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH23" s="15">
+      <c r="BH23" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="15">
         <v>200001</v>
       </c>
-      <c r="BI23" s="17">
+      <c r="BJ23" s="16">
         <v>100</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:61">
+    <row r="24" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C24" s="7">
         <v>2000002</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E24" s="7">
-        <v>2000002</v>
+      <c r="E24" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="F24" s="7">
         <v>2000002</v>
       </c>
       <c r="G24" s="7">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="s">
+        <v>2000002</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="8">
+      <c r="J24" s="8">
         <v>2</v>
       </c>
-      <c r="J24" s="8">
-        <v>1</v>
-      </c>
-      <c r="K24" s="7">
+      <c r="K24" s="8">
+        <v>1</v>
+      </c>
+      <c r="L24" s="7">
         <v>5</v>
       </c>
-      <c r="L24" s="7">
-        <v>1</v>
-      </c>
-      <c r="M24" s="7" t="s">
+      <c r="M24" s="7">
+        <v>1</v>
+      </c>
+      <c r="N24" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N24" s="7">
-        <v>0</v>
-      </c>
       <c r="O24" s="7">
-        <v>1</v>
-      </c>
-      <c r="P24" s="8">
-        <v>3200</v>
+        <v>0</v>
+      </c>
+      <c r="P24" s="7">
+        <v>1</v>
       </c>
       <c r="Q24" s="8">
         <v>3200</v>
       </c>
       <c r="R24" s="8">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="S24" s="8">
         <v>1600</v>
@@ -7066,47 +6655,47 @@
         <v>1600</v>
       </c>
       <c r="Z24" s="8">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="AA24" s="8">
         <v>3000</v>
       </c>
       <c r="AB24" s="8">
-        <v>1.5</v>
+        <v>3000</v>
       </c>
       <c r="AC24" s="8">
         <v>1.5</v>
       </c>
       <c r="AD24" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" s="8">
         <v>5000</v>
       </c>
-      <c r="AE24" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF24" s="8">
         <v>1000</v>
       </c>
       <c r="AG24" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH24" s="8">
         <v>350</v>
       </c>
       <c r="AI24" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ24" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ24" s="8">
-        <v>0</v>
-      </c>
       <c r="AK24" s="8">
         <v>0</v>
       </c>
       <c r="AL24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM24" s="8">
-        <v>0</v>
-      </c>
       <c r="AN24" s="8">
         <v>0</v>
       </c>
@@ -7114,112 +6703,115 @@
         <v>0</v>
       </c>
       <c r="AP24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="8">
         <v>6</v>
       </c>
-      <c r="AQ24" s="8">
-        <v>1.1</v>
-      </c>
       <c r="AR24" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS24" s="8">
         <v>6</v>
       </c>
-      <c r="AS24" s="8">
+      <c r="AT24" s="8">
         <v>132</v>
-      </c>
-      <c r="AT24" s="8">
-        <v>25</v>
       </c>
       <c r="AU24" s="8">
         <v>25</v>
       </c>
       <c r="AV24" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW24" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX24" s="12">
+      <c r="AX24" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY24" s="12">
         <v>3</v>
       </c>
-      <c r="AY24" s="8">
+      <c r="AZ24" s="8">
         <v>15</v>
       </c>
-      <c r="AZ24" s="12">
+      <c r="BA24" s="12">
         <v>10</v>
       </c>
-      <c r="BA24" s="8">
+      <c r="BB24" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB24" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC24" s="8"/>
-      <c r="BD24" s="8">
-        <v>0</v>
-      </c>
+      <c r="BC24" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="8"/>
       <c r="BE24" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF24" s="8">
         <v>70000012</v>
       </c>
-      <c r="BF24" s="18" t="s">
+      <c r="BG24" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="BG24" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH24" s="15">
+      <c r="BH24" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="15">
         <v>200002</v>
       </c>
-      <c r="BI24" s="17">
+      <c r="BJ24" s="16">
         <v>100</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:61">
+    <row r="25" spans="3:62" ht="20.100000000000001" customHeight="1">
       <c r="C25" s="7">
         <v>2000003</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E25" s="7">
-        <v>2000003</v>
+      <c r="E25" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="F25" s="7">
         <v>2000003</v>
       </c>
       <c r="G25" s="7">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8" t="s">
+        <v>2000003</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I25" s="8">
+      <c r="J25" s="8">
         <v>2</v>
       </c>
-      <c r="J25" s="8">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7">
+      <c r="K25" s="8">
+        <v>1</v>
+      </c>
+      <c r="L25" s="7">
         <v>5</v>
       </c>
-      <c r="L25" s="7">
-        <v>1</v>
-      </c>
-      <c r="M25" s="7" t="s">
+      <c r="M25" s="7">
+        <v>1</v>
+      </c>
+      <c r="N25" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N25" s="7">
-        <v>0</v>
-      </c>
       <c r="O25" s="7">
-        <v>1</v>
-      </c>
-      <c r="P25" s="8">
-        <v>3200</v>
+        <v>0</v>
+      </c>
+      <c r="P25" s="7">
+        <v>1</v>
       </c>
       <c r="Q25" s="8">
         <v>3200</v>
       </c>
       <c r="R25" s="8">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="S25" s="8">
         <v>1600</v>
@@ -7243,47 +6835,47 @@
         <v>1600</v>
       </c>
       <c r="Z25" s="8">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="AA25" s="8">
         <v>3000</v>
       </c>
       <c r="AB25" s="8">
-        <v>1.5</v>
+        <v>3000</v>
       </c>
       <c r="AC25" s="8">
         <v>1.5</v>
       </c>
       <c r="AD25" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="AE25" s="8">
         <v>5000</v>
       </c>
-      <c r="AE25" s="8">
-        <v>1000</v>
-      </c>
       <c r="AF25" s="8">
         <v>1000</v>
       </c>
       <c r="AG25" s="8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AH25" s="8">
         <v>350</v>
       </c>
       <c r="AI25" s="8">
+        <v>350</v>
+      </c>
+      <c r="AJ25" s="8">
         <v>0.05</v>
       </c>
-      <c r="AJ25" s="8">
-        <v>0</v>
-      </c>
       <c r="AK25" s="8">
         <v>0</v>
       </c>
       <c r="AL25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="8">
         <v>0.05</v>
       </c>
-      <c r="AM25" s="8">
-        <v>0</v>
-      </c>
       <c r="AN25" s="8">
         <v>0</v>
       </c>
@@ -7291,70 +6883,74 @@
         <v>0</v>
       </c>
       <c r="AP25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="8">
         <v>6</v>
       </c>
-      <c r="AQ25" s="8">
+      <c r="AR25" s="8">
         <v>0.8</v>
       </c>
-      <c r="AR25" s="8">
+      <c r="AS25" s="8">
         <v>2</v>
       </c>
-      <c r="AS25" s="8">
+      <c r="AT25" s="8">
         <v>132</v>
-      </c>
-      <c r="AT25" s="8">
-        <v>25</v>
       </c>
       <c r="AU25" s="8">
         <v>25</v>
       </c>
       <c r="AV25" s="8">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="AW25" s="8">
         <v>7.5</v>
       </c>
-      <c r="AX25" s="12">
+      <c r="AX25" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="AY25" s="12">
         <v>3</v>
       </c>
-      <c r="AY25" s="8">
+      <c r="AZ25" s="8">
         <v>15</v>
       </c>
-      <c r="AZ25" s="12">
+      <c r="BA25" s="12">
         <v>10</v>
       </c>
-      <c r="BA25" s="8">
+      <c r="BB25" s="8">
         <v>0.1</v>
       </c>
-      <c r="BB25" s="8">
-        <v>1</v>
-      </c>
-      <c r="BC25" s="8"/>
-      <c r="BD25" s="8">
-        <v>0</v>
-      </c>
+      <c r="BC25" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="8"/>
       <c r="BE25" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF25" s="8">
         <v>70000011</v>
       </c>
-      <c r="BF25" s="18" t="s">
+      <c r="BG25" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="BG25" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH25" s="17">
+      <c r="BH25" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="16">
         <v>200003</v>
       </c>
-      <c r="BI25" s="17">
+      <c r="BJ25" s="16">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF09DD98-60F3-4C0B-92CF-C609F9DD1C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6BB789-3A68-4F6D-A1F8-A57F336591C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,15 +926,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Little Duck Duck</t>
-  </si>
-  <si>
-    <t>Little Squirrel</t>
-  </si>
-  <si>
-    <t>Little gray wolf</t>
-  </si>
-  <si>
     <t>Cactus</t>
   </si>
   <si>
@@ -953,43 +944,59 @@
     <t>Thunder Pig</t>
   </si>
   <si>
+    <t>Magic Elves</t>
+  </si>
+  <si>
+    <t>Magic Doll</t>
+  </si>
+  <si>
+    <t>Naughty Guy</t>
+  </si>
+  <si>
+    <t>Loving Spirit</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spirit Fox</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ironclad</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light Angel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>Octopus Lady</t>
-  </si>
-  <si>
-    <t>Magic Elves</t>
-  </si>
-  <si>
-    <t>Magic Doll</t>
-  </si>
-  <si>
-    <t>Naughty Guy</t>
-  </si>
-  <si>
-    <t>Light Angel</t>
-  </si>
-  <si>
-    <t>Ironclad Warrior</t>
-  </si>
-  <si>
-    <t>Spirit Fox Demon</t>
-  </si>
-  <si>
-    <t>Loving Spirit</t>
-  </si>
-  <si>
-    <t>Legendary: Elf Deer</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Legendary: Yuguang Qingqing</t>
+    <t>Duck Duck</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Legendary: Immortal Realm</t>
+    <t>Squirrel</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>c</t>
+    <t>Gray wolf</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary:Deer</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary:Ghost</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary:Dragon</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2732,7 +2739,8 @@
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="5" width="14.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.75" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="11.875" style="2" customWidth="1"/>
     <col min="9" max="9" width="20" style="2" customWidth="1"/>
     <col min="10" max="14" width="11.875" style="2" customWidth="1"/>
@@ -2761,7 +2769,7 @@
     <row r="2" spans="3:62" ht="13.5" customHeight="1">
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="3:62" ht="20.100000000000001" customHeight="1">
@@ -3318,7 +3326,7 @@
         <v>113</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F6" s="7">
         <v>1000101</v>
@@ -3500,7 +3508,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F7" s="7">
         <v>1000201</v>
@@ -3682,7 +3690,7 @@
         <v>124</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F8" s="7">
         <v>1000301</v>
@@ -3864,7 +3872,7 @@
         <v>127</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F9" s="7">
         <v>1000401</v>
@@ -4046,7 +4054,7 @@
         <v>130</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F10" s="7">
         <v>1000501</v>
@@ -4228,7 +4236,7 @@
         <v>135</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F11" s="7">
         <v>1000601</v>
@@ -4410,7 +4418,7 @@
         <v>138</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F12" s="7">
         <v>1000701</v>
@@ -4592,7 +4600,7 @@
         <v>141</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F13" s="7">
         <v>1000801</v>
@@ -4774,7 +4782,7 @@
         <v>145</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F14" s="7">
         <v>1000901</v>
@@ -4956,7 +4964,7 @@
         <v>148</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F15" s="7">
         <v>1001001</v>
@@ -5138,7 +5146,7 @@
         <v>153</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F16" s="7">
         <v>1001101</v>
@@ -5320,7 +5328,7 @@
         <v>157</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F17" s="7">
         <v>1001201</v>
@@ -5502,7 +5510,7 @@
         <v>161</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F18" s="7">
         <v>1001301</v>
@@ -5866,7 +5874,7 @@
         <v>169</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F20" s="7">
         <v>1009101</v>
@@ -6048,7 +6056,7 @@
         <v>173</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F21" s="7">
         <v>1009201</v>
@@ -6230,7 +6238,7 @@
         <v>177</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F22" s="7">
         <v>1009301</v>
@@ -6412,7 +6420,7 @@
         <v>181</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F23" s="7">
         <v>2000001</v>
@@ -6592,7 +6600,7 @@
         <v>183</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F24" s="7">
         <v>2000002</v>
@@ -6772,7 +6780,7 @@
         <v>185</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7">
         <v>2000003</v>
